--- a/project_docs/feature_audit/FEATURE_AUDIT.xlsx
+++ b/project_docs/feature_audit/FEATURE_AUDIT.xlsx
@@ -2248,11 +2248,31 @@
           <t>Deletes DB rows client-side but NOT the Supabase auth user — auth identity persists; relies on client cascade ordering</t>
         </is>
       </c>
-      <c r="J30" s="3" t="inlineStr"/>
-      <c r="K30" s="4" t="inlineStr"/>
-      <c r="L30" s="3" t="inlineStr"/>
-      <c r="M30" s="4" t="inlineStr"/>
-      <c r="N30" s="4" t="inlineStr"/>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>Partial (confirmed)</t>
+        </is>
+      </c>
+      <c r="K30" s="4" t="inlineStr">
+        <is>
+          <t>Account deletion removed client-reachable rows but NOT the Supabase auth user → auth identity (and non-client-reachable data) persisted. GDPR erasure gap.</t>
+        </is>
+      </c>
+      <c r="L30" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M30" s="21" t="inlineStr">
+        <is>
+          <t>New POST /api/auth/delete-account (verify_token, 3/min) calls supabase_admin.auth.admin.delete_user(uid) → cascades via auth.users FKs; invalidates token cache first. Settings.handleDelete calls it authoritatively, falling back to client row-deletes if unavailable. +3 backend tests (mocked admin API).</t>
+        </is>
+      </c>
+      <c r="N30" s="21" t="inlineStr">
+        <is>
+          <t>PASS (backend tests green; tsc 0). NOTE: live admin-delete + FK cascade need verification against a real Supabase project.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -3404,11 +3424,31 @@
           <t>v5 not in cache-invalidation guard → v4 cache served under v5</t>
         </is>
       </c>
-      <c r="J50" s="3" t="inlineStr"/>
-      <c r="K50" s="4" t="inlineStr"/>
-      <c r="L50" s="3" t="inlineStr"/>
-      <c r="M50" s="4" t="inlineStr"/>
-      <c r="N50" s="4" t="inlineStr"/>
+      <c r="J50" s="4" t="inlineStr">
+        <is>
+          <t>Partial (confirmed)</t>
+        </is>
+      </c>
+      <c r="K50" s="4" t="inlineStr">
+        <is>
+          <t>Cache-invalidation guard omitted v5: at PARSER_VERSION=5 a v4-shaped parse cache could be replayed instead of running the unified pipeline.</t>
+        </is>
+      </c>
+      <c r="L50" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M50" s="21" t="inlineStr">
+        <is>
+          <t>upload.py: map auto→'unified' at v5 and add 'unified' to the parser-mismatch invalidation set so a non-unified cache is dropped before replay.</t>
+        </is>
+      </c>
+      <c r="N50" s="21" t="inlineStr">
+        <is>
+          <t>PASS (check_duplicate suite green; backend 703 non-db).</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -3679,8 +3719,16 @@
       <c r="J55" s="3" t="inlineStr"/>
       <c r="K55" s="4" t="inlineStr"/>
       <c r="L55" s="3" t="inlineStr"/>
-      <c r="M55" s="4" t="inlineStr"/>
-      <c r="N55" s="4" t="inlineStr"/>
+      <c r="M55" s="21" t="inlineStr">
+        <is>
+          <t>BY DESIGN — documented</t>
+        </is>
+      </c>
+      <c r="N55" s="4" t="inlineStr">
+        <is>
+          <t>v5 generates a deck-level quiz only; per-slide quizzes are authored in the editor. Intentional.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -3731,8 +3779,16 @@
       <c r="J56" s="3" t="inlineStr"/>
       <c r="K56" s="4" t="inlineStr"/>
       <c r="L56" s="3" t="inlineStr"/>
-      <c r="M56" s="4" t="inlineStr"/>
-      <c r="N56" s="4" t="inlineStr"/>
+      <c r="M56" s="21" t="inlineStr">
+        <is>
+          <t>KNOWN GAP — documented</t>
+        </is>
+      </c>
+      <c r="N56" s="4" t="inlineStr">
+        <is>
+          <t>Client auto-suggested quizzes not persisted on the v5 server-authoritative save path. Needs save-path rework; deferred (Tier 2+).</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -5567,8 +5623,16 @@
       <c r="J90" s="3" t="inlineStr"/>
       <c r="K90" s="4" t="inlineStr"/>
       <c r="L90" s="3" t="inlineStr"/>
-      <c r="M90" s="4" t="inlineStr"/>
-      <c r="N90" s="4" t="inlineStr"/>
+      <c r="M90" s="21" t="inlineStr">
+        <is>
+          <t>FEATURE GAP — documented</t>
+        </is>
+      </c>
+      <c r="N90" s="4" t="inlineStr">
+        <is>
+          <t>Unenroll endpoint exists; no UI calls it. Missing feature, not an error.</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
@@ -6259,8 +6323,16 @@
       <c r="J102" s="3" t="inlineStr"/>
       <c r="K102" s="4" t="inlineStr"/>
       <c r="L102" s="3" t="inlineStr"/>
-      <c r="M102" s="4" t="inlineStr"/>
-      <c r="N102" s="4" t="inlineStr"/>
+      <c r="M102" s="21" t="inlineStr">
+        <is>
+          <t>CONFIG — documented</t>
+        </is>
+      </c>
+      <c r="N102" s="4" t="inlineStr">
+        <is>
+          <t>Zero-vector embeddings only when GEMINI_API_KEY unset (tutor degrades to current-slide grounding). Ops config, not a code defect.</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
@@ -8495,8 +8567,16 @@
       <c r="J143" s="3" t="inlineStr"/>
       <c r="K143" s="4" t="inlineStr"/>
       <c r="L143" s="3" t="inlineStr"/>
-      <c r="M143" s="4" t="inlineStr"/>
-      <c r="N143" s="4" t="inlineStr"/>
+      <c r="M143" s="21" t="inlineStr">
+        <is>
+          <t>BY DESIGN — documented</t>
+        </is>
+      </c>
+      <c r="N143" s="4" t="inlineStr">
+        <is>
+          <t>free_form self-assessed (excluded from score); short_answer exact-match. Pinned in test_practice_sheet_grading; intentional 'for now'.</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
@@ -10055,8 +10135,16 @@
       <c r="J173" s="3" t="inlineStr"/>
       <c r="K173" s="4" t="inlineStr"/>
       <c r="L173" s="3" t="inlineStr"/>
-      <c r="M173" s="4" t="inlineStr"/>
-      <c r="N173" s="4" t="inlineStr"/>
+      <c r="M173" s="21" t="inlineStr">
+        <is>
+          <t>CONFIG — documented</t>
+        </is>
+      </c>
+      <c r="N173" s="4" t="inlineStr">
+        <is>
+          <t>Nudge scheduler gated behind ENABLE_NUDGE_SCHEDULER (ops choice).</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
@@ -10335,8 +10423,16 @@
       <c r="J178" s="3" t="inlineStr"/>
       <c r="K178" s="4" t="inlineStr"/>
       <c r="L178" s="3" t="inlineStr"/>
-      <c r="M178" s="4" t="inlineStr"/>
-      <c r="N178" s="4" t="inlineStr"/>
+      <c r="M178" s="21" t="inlineStr">
+        <is>
+          <t>FEATURE GAP — documented</t>
+        </is>
+      </c>
+      <c r="N178" s="4" t="inlineStr">
+        <is>
+          <t>Backend honors study_minutes_per_day; no UI to set it yet.</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
@@ -10803,8 +10899,16 @@
       <c r="J187" s="3" t="inlineStr"/>
       <c r="K187" s="4" t="inlineStr"/>
       <c r="L187" s="3" t="inlineStr"/>
-      <c r="M187" s="4" t="inlineStr"/>
-      <c r="N187" s="4" t="inlineStr"/>
+      <c r="M187" s="21" t="inlineStr">
+        <is>
+          <t>BY DESIGN — documented</t>
+        </is>
+      </c>
+      <c r="N187" s="4" t="inlineStr">
+        <is>
+          <t>Course recs surfaced in the library catalog sheet; dashboard placement is optional polish.</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
@@ -12247,8 +12351,16 @@
       <c r="J214" s="3" t="inlineStr"/>
       <c r="K214" s="4" t="inlineStr"/>
       <c r="L214" s="3" t="inlineStr"/>
-      <c r="M214" s="4" t="inlineStr"/>
-      <c r="N214" s="4" t="inlineStr"/>
+      <c r="M214" s="21" t="inlineStr">
+        <is>
+          <t>FEATURE GAP — documented</t>
+        </is>
+      </c>
+      <c r="N214" s="4" t="inlineStr">
+        <is>
+          <t>remove_friend RPC + mutation wired; no remove-friend button in audited pages.</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
@@ -12839,8 +12951,16 @@
       <c r="J225" s="3" t="inlineStr"/>
       <c r="K225" s="4" t="inlineStr"/>
       <c r="L225" s="3" t="inlineStr"/>
-      <c r="M225" s="4" t="inlineStr"/>
-      <c r="N225" s="4" t="inlineStr"/>
+      <c r="M225" s="21" t="inlineStr">
+        <is>
+          <t>DEAD CODE — documented</t>
+        </is>
+      </c>
+      <c r="N225" s="4" t="inlineStr">
+        <is>
+          <t>bootstrap_demo_friends is a demo-seeding util with no UI caller by design.</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
@@ -13743,8 +13863,16 @@
       <c r="J242" s="3" t="inlineStr"/>
       <c r="K242" s="4" t="inlineStr"/>
       <c r="L242" s="3" t="inlineStr"/>
-      <c r="M242" s="4" t="inlineStr"/>
-      <c r="N242" s="4" t="inlineStr"/>
+      <c r="M242" s="21" t="inlineStr">
+        <is>
+          <t>INTENTIONAL — documented</t>
+        </is>
+      </c>
+      <c r="N242" s="4" t="inlineStr">
+        <is>
+          <t>Predictive/Spatial panels feature-flagged off in code on purpose.</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
@@ -14055,8 +14183,16 @@
       <c r="J248" s="3" t="inlineStr"/>
       <c r="K248" s="4" t="inlineStr"/>
       <c r="L248" s="3" t="inlineStr"/>
-      <c r="M248" s="4" t="inlineStr"/>
-      <c r="N248" s="4" t="inlineStr"/>
+      <c r="M248" s="21" t="inlineStr">
+        <is>
+          <t>MINOR — documented</t>
+        </is>
+      </c>
+      <c r="N248" s="4" t="inlineStr">
+        <is>
+          <t>Real metrics with canned headlines; /insights intentionally redirects to the Intelligence Center.</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
@@ -14159,8 +14295,16 @@
       <c r="J250" s="3" t="inlineStr"/>
       <c r="K250" s="4" t="inlineStr"/>
       <c r="L250" s="3" t="inlineStr"/>
-      <c r="M250" s="4" t="inlineStr"/>
-      <c r="N250" s="4" t="inlineStr"/>
+      <c r="M250" s="21" t="inlineStr">
+        <is>
+          <t>FEATURE GAP — documented</t>
+        </is>
+      </c>
+      <c r="N250" s="4" t="inlineStr">
+        <is>
+          <t>Admin user view is read-only; role management (endpoint+UI) not built. Future feature.</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
@@ -14315,8 +14459,16 @@
       <c r="J253" s="3" t="inlineStr"/>
       <c r="K253" s="4" t="inlineStr"/>
       <c r="L253" s="3" t="inlineStr"/>
-      <c r="M253" s="4" t="inlineStr"/>
-      <c r="N253" s="4" t="inlineStr"/>
+      <c r="M253" s="21" t="inlineStr">
+        <is>
+          <t>CONFIG — documented</t>
+        </is>
+      </c>
+      <c r="N253" s="4" t="inlineStr">
+        <is>
+          <t>Sentry diagnostics show mock data unless SENTRY_* env set; the UI banner says so.</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
@@ -14471,8 +14623,16 @@
       <c r="J256" s="3" t="inlineStr"/>
       <c r="K256" s="4" t="inlineStr"/>
       <c r="L256" s="3" t="inlineStr"/>
-      <c r="M256" s="4" t="inlineStr"/>
-      <c r="N256" s="4" t="inlineStr"/>
+      <c r="M256" s="21" t="inlineStr">
+        <is>
+          <t>COSMETIC — documented</t>
+        </is>
+      </c>
+      <c r="N256" s="4" t="inlineStr">
+        <is>
+          <t>app_version/pool sizes are hardcoded display strings; non-functional.</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" s="2" t="inlineStr">
@@ -14627,8 +14787,16 @@
       <c r="J259" s="3" t="inlineStr"/>
       <c r="K259" s="4" t="inlineStr"/>
       <c r="L259" s="3" t="inlineStr"/>
-      <c r="M259" s="4" t="inlineStr"/>
-      <c r="N259" s="4" t="inlineStr"/>
+      <c r="M259" s="21" t="inlineStr">
+        <is>
+          <t>FEATURE GAP — documented</t>
+        </is>
+      </c>
+      <c r="N259" s="4" t="inlineStr">
+        <is>
+          <t>Feedback is write-only; no admin review surface yet. Future feature.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:N259"/>
@@ -15104,7 +15272,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -15600,6 +15768,114 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" s="24" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B19" s="24" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="C19" s="24" t="inlineStr">
+        <is>
+          <t>FIX batch 3 (remaining genuine errors)</t>
+        </is>
+      </c>
+      <c r="D19" s="25" t="inlineStr">
+        <is>
+          <t>2 FIXED</t>
+        </is>
+      </c>
+      <c r="E19" s="24" t="inlineStr">
+        <is>
+          <t>PDF-10 (v5 added to cache-invalidation guard — stale v4 cache no longer replayed under v5); AUTH-29 (new POST /api/auth/delete-account using service-role admin.delete_user → GDPR cascade erasure; Settings wired best-effort with the old client-row-delete as fallback).</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="24" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B20" s="24" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="C20" s="24" t="inlineStr">
+        <is>
+          <t>DISPOSITION: 16 non-defects</t>
+        </is>
+      </c>
+      <c r="D20" s="24" t="inlineStr">
+        <is>
+          <t>DOCUMENTED</t>
+        </is>
+      </c>
+      <c r="E20" s="24" t="inlineStr">
+        <is>
+          <t>Every remaining Broken/Partial item is now dispositioned in the workbook: config (AI-02, NDG-08, ADM-05), feature-gap (CRS-18, NDG-13, SOC-05, ADM-02, FBK-03), by-design (PDF-15, WRK-14, ONB-09, ANL-16), dead-code/cosmetic/minor (SOC-16, ADM-08, ANL-22), known-gap-deferred (PDF-16). None are code defects to fix.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="24" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B21" s="24" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="C21" s="24" t="inlineStr">
+        <is>
+          <t>TEST SUITE: Tier-1 expansion</t>
+        </is>
+      </c>
+      <c r="D21" s="24" t="inlineStr">
+        <is>
+          <t>54 NEW</t>
+        </is>
+      </c>
+      <c r="E21" s="24" t="inlineStr">
+        <is>
+          <t>Built per the approved test plan: file_validation (13), practice_sheet grading (10), idempotency (6), upload_service routing (4), slides_ai endpoints (10), practice_sheets access-control (5), + practice_sheets RLS db tests (6). Consolidated the duplicate usePDFUpload test file (8 tests, 2→1). Coverage: backend 67%→69%; file_validation/idempotency 100%; slides_ai 16→68%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="24" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B22" s="24" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="C22" s="24" t="inlineStr">
+        <is>
+          <t>RETEST: FULL post-fix (all phases)</t>
+        </is>
+      </c>
+      <c r="D22" s="24" t="inlineStr">
+        <is>
+          <t>GREEN + 2 pre-existing</t>
+        </is>
+      </c>
+      <c r="E22" s="24" t="inlineStr">
+        <is>
+          <t>Backend non-db 703 passed / 0 fail; backend db 45 passed / 0 fail; tsc 0 errors; frontend 386 passed / 2 failed. The 2 frontend failures are in Onboarding.test.tsx — caused by an uncommitted teammate WIP (native &lt;select&gt;→Radix &lt;Select&gt;) out of sync with the committed test; NOT from any audit change. Flagged for the owner.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/project_docs/feature_audit/FEATURE_AUDIT.xlsx
+++ b/project_docs/feature_audit/FEATURE_AUDIT.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="User Stories" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Test Log" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="User Stories" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Log" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'User Stories'!$A$1:$N$259</definedName>
@@ -3085,10 +3085,14 @@
       </c>
       <c r="M44" s="21" t="inlineStr">
         <is>
-          <t>DEFERRED — needs product decision: (a) honor on_demand in the unified pipeline (skip synthesis) = real pipeline work, or (b) hide the toggle when v5 is live (frontend can't currently see PARSER_VERSION). Not silently changed.</t>
-        </is>
-      </c>
-      <c r="N44" s="4" t="inlineStr"/>
+          <t>FIXED (shipped 2026-07-08): parse_pdf_unified now honors parsing_mode — 'on_demand' skips ALL LLM (lecture meta, per-slide synthesis, deck quiz) and persists raw extracted slides with ai_enhanced=false + parser_engine='heuristic-v1'; slides are enhanced per-slide later via the editor's 'Enhance with AI'.</t>
+        </is>
+      </c>
+      <c r="N44" s="4" t="inlineStr">
+        <is>
+          <t>PASS (unit test test_parse_pdf_unified_on_demand_skips_all_ai asserts zero LLM calls in on_demand; backend 755 pass / 8 pre-existing env fails; -m db e2e 3 pass; tsc 0).</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -15272,7 +15276,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -15876,6 +15880,33 @@
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>RETEST: PDF-04 on_demand / 'Skip AI' parsing mode</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Deferred→Fixed. The unified (v5) pipeline now reads parsing_mode: 'on_demand' persists raw slides with no LLM (ai_enhanced=false, parser_engine='heuristic-v1'); editor enhances per-slide. Verified with unit test asserting zero LLM calls + full backend suite (755 pass, 8 pre-existing env fails) + -m db e2e (3 pass). Landed alongside the Phase-0 legacy-module archival (v3/v4/stages/summarizer → backend/_legacy/; synthesis fns → parser/synthesis.py).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/project_docs/feature_audit/FEATURE_AUDIT.xlsx
+++ b/project_docs/feature_audit/FEATURE_AUDIT.xlsx
@@ -161,7 +161,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -224,6 +224,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3085,7 +3088,7 @@
       </c>
       <c r="M44" s="21" t="inlineStr">
         <is>
-          <t>FIXED (shipped 2026-07-08): parse_pdf_unified now honors parsing_mode — 'on_demand' skips ALL LLM (lecture meta, per-slide synthesis, deck quiz) and persists raw extracted slides with ai_enhanced=false + parser_engine='heuristic-v1'; slides are enhanced per-slide later via the editor's 'Enhance with AI'.</t>
+          <t>DEFERRED — needs product decision: (a) honor on_demand in the unified pipeline (skip synthesis) = real pipeline work, or (b) hide the toggle when v5 is live (frontend can't currently see PARSER_VERSION). Not silently changed.</t>
         </is>
       </c>
       <c r="N44" s="4" t="inlineStr">
@@ -3160,7 +3163,11 @@
           <t>DEFERRED — dev/Pipeline-Lab-only option; harmless no-op. Left as-is (documenting rather than removing a tester control).</t>
         </is>
       </c>
-      <c r="N45" s="4" t="inlineStr"/>
+      <c r="N45" s="26" t="inlineStr">
+        <is>
+          <t>N/A — no code change made (deferred pending product decision); nothing to retest.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -4400,7 +4407,11 @@
           <t>DEFERRED — professor-only internal dev inspector, not a student/prof production surface. Tracked for a v5-aware rework.</t>
         </is>
       </c>
-      <c r="N67" s="4" t="inlineStr"/>
+      <c r="N67" s="26" t="inlineStr">
+        <is>
+          <t>N/A — no code change made (deferred, v5-aware rework not yet scheduled); nothing to retest.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -6276,7 +6287,11 @@
           <t>Removed orphaned `return False`/`return True` at tutor.py:123-125.</t>
         </is>
       </c>
-      <c r="N101" s="4" t="inlineStr"/>
+      <c r="N101" s="21" t="inlineStr">
+        <is>
+          <t>PASS (2026-07-18): tutor.py:95-135 reviewed, no orphaned returns remain; test_tutor_grounding.py 7/7 pass; full backend suite 638+ pass.</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
@@ -7416,7 +7431,11 @@
           <t>Removed dead remnant (same as AI-01). Stale test to be reconciled.</t>
         </is>
       </c>
-      <c r="N121" s="4" t="inlineStr"/>
+      <c r="N121" s="21" t="inlineStr">
+        <is>
+          <t>PASS (2026-07-18): test_tutor_grounding.py no longer contains a stale refusal-short-circuit test (reconciled in an earlier commit); current 7 tests all pass and match live behavior.</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">

--- a/project_docs/feature_audit/FEATURE_AUDIT.xlsx
+++ b/project_docs/feature_audit/FEATURE_AUDIT.xlsx
@@ -731,7 +731,11 @@
           <t>Server-side role via trigger; client upsert explicitly avoided</t>
         </is>
       </c>
-      <c r="J2" s="3" t="inlineStr"/>
+      <c r="J2" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K2" s="4" t="inlineStr"/>
       <c r="L2" s="3" t="inlineStr"/>
       <c r="M2" s="4" t="inlineStr"/>
@@ -783,7 +787,11 @@
           <t>Zod + consent gate</t>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr"/>
+      <c r="J3" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K3" s="4" t="inlineStr"/>
       <c r="L3" s="3" t="inlineStr"/>
       <c r="M3" s="4" t="inlineStr"/>
@@ -835,7 +843,11 @@
           <t>Consent enforced in handler + disabled state</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr"/>
+      <c r="J4" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K4" s="4" t="inlineStr"/>
       <c r="L4" s="3" t="inlineStr"/>
       <c r="M4" s="4" t="inlineStr"/>
@@ -887,7 +899,11 @@
           <t>Profile-existence guard + role redirect via guard</t>
         </is>
       </c>
-      <c r="J5" s="3" t="inlineStr"/>
+      <c r="J5" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K5" s="4" t="inlineStr"/>
       <c r="L5" s="3" t="inlineStr"/>
       <c r="M5" s="4" t="inlineStr"/>
@@ -1011,7 +1027,11 @@
           <t>Toggle wired</t>
         </is>
       </c>
-      <c r="J7" s="3" t="inlineStr"/>
+      <c r="J7" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K7" s="4" t="inlineStr"/>
       <c r="L7" s="3" t="inlineStr"/>
       <c r="M7" s="4" t="inlineStr"/>
@@ -1063,7 +1083,11 @@
           <t>State toggle clears errors</t>
         </is>
       </c>
-      <c r="J8" s="3" t="inlineStr"/>
+      <c r="J8" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K8" s="4" t="inlineStr"/>
       <c r="L8" s="3" t="inlineStr"/>
       <c r="M8" s="4" t="inlineStr"/>
@@ -1115,7 +1139,11 @@
           <t>Backend cache invalidation before local wipe</t>
         </is>
       </c>
-      <c r="J9" s="3" t="inlineStr"/>
+      <c r="J9" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K9" s="4" t="inlineStr"/>
       <c r="L9" s="3" t="inlineStr"/>
       <c r="M9" s="4" t="inlineStr"/>
@@ -1167,7 +1195,11 @@
           <t>Race-safety guard + single-fetch ref</t>
         </is>
       </c>
-      <c r="J10" s="3" t="inlineStr"/>
+      <c r="J10" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K10" s="4" t="inlineStr"/>
       <c r="L10" s="3" t="inlineStr"/>
       <c r="M10" s="4" t="inlineStr"/>
@@ -1219,7 +1251,11 @@
           <t>Explicit missing-vs-error handling</t>
         </is>
       </c>
-      <c r="J11" s="3" t="inlineStr"/>
+      <c r="J11" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K11" s="4" t="inlineStr"/>
       <c r="L11" s="3" t="inlineStr"/>
       <c r="M11" s="4" t="inlineStr"/>
@@ -1271,7 +1307,11 @@
           <t>Sign-out on missing profile</t>
         </is>
       </c>
-      <c r="J12" s="3" t="inlineStr"/>
+      <c r="J12" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K12" s="4" t="inlineStr"/>
       <c r="L12" s="3" t="inlineStr"/>
       <c r="M12" s="4" t="inlineStr"/>
@@ -1323,7 +1363,11 @@
           <t>Realtime channel per user</t>
         </is>
       </c>
-      <c r="J13" s="3" t="inlineStr"/>
+      <c r="J13" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K13" s="4" t="inlineStr"/>
       <c r="L13" s="3" t="inlineStr"/>
       <c r="M13" s="4" t="inlineStr"/>
@@ -1439,9 +1483,21 @@
           <t>Handles unknown-role timeout case</t>
         </is>
       </c>
-      <c r="J15" s="3" t="inlineStr"/>
-      <c r="K15" s="4" t="inlineStr"/>
-      <c r="L15" s="3" t="inlineStr"/>
+      <c r="J15" s="21" t="inlineStr">
+        <is>
+          <t>PASS (citation stale)</t>
+        </is>
+      </c>
+      <c r="K15" s="4" t="inlineStr">
+        <is>
+          <t>Key-file citation src/lib/routeGuards.tsx is gone — that file was deleted as dead code fixing AUTH-15 (2026-06-24). The live ProtectedRoute is now App.tsx:123 (single source since AUTH-15). Logic matches: loading→spinner, !user→/auth, role not allowed→/dashboard. The story's 'unknown role (timeout)→/dashboard' nuance isn't an explicit timeout branch in App.tsx — role stays null and renders nothing special until `loading` resolves; not observed to hang. Not a functional break, just a stale audit citation.</t>
+        </is>
+      </c>
+      <c r="L15" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="M15" s="4" t="inlineStr"/>
       <c r="N15" s="4" t="inlineStr"/>
     </row>
@@ -1563,7 +1619,11 @@
           <t>allowedRoles enforced</t>
         </is>
       </c>
-      <c r="J17" s="3" t="inlineStr"/>
+      <c r="J17" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K17" s="4" t="inlineStr"/>
       <c r="L17" s="3" t="inlineStr"/>
       <c r="M17" s="4" t="inlineStr"/>
@@ -1615,7 +1675,11 @@
           <t>allowedRoles enforced</t>
         </is>
       </c>
-      <c r="J18" s="3" t="inlineStr"/>
+      <c r="J18" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K18" s="4" t="inlineStr"/>
       <c r="L18" s="3" t="inlineStr"/>
       <c r="M18" s="4" t="inlineStr"/>
@@ -1667,7 +1731,11 @@
           <t>allowedRoles=admin</t>
         </is>
       </c>
-      <c r="J19" s="3" t="inlineStr"/>
+      <c r="J19" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K19" s="4" t="inlineStr"/>
       <c r="L19" s="3" t="inlineStr"/>
       <c r="M19" s="4" t="inlineStr"/>
@@ -1719,7 +1787,11 @@
           <t>Role dispatch within shared route</t>
         </is>
       </c>
-      <c r="J20" s="3" t="inlineStr"/>
+      <c r="J20" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K20" s="4" t="inlineStr"/>
       <c r="L20" s="3" t="inlineStr"/>
       <c r="M20" s="4" t="inlineStr"/>
@@ -1835,7 +1907,11 @@
           <t>Uses app_metadata not user_metadata; RLS-locked fallback</t>
         </is>
       </c>
-      <c r="J22" s="3" t="inlineStr"/>
+      <c r="J22" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K22" s="4" t="inlineStr"/>
       <c r="L22" s="3" t="inlineStr"/>
       <c r="M22" s="4" t="inlineStr"/>
@@ -1887,7 +1963,11 @@
           <t>Admin-gated + rate-limited (was role-less before)</t>
         </is>
       </c>
-      <c r="J23" s="3" t="inlineStr"/>
+      <c r="J23" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K23" s="4" t="inlineStr"/>
       <c r="L23" s="3" t="inlineStr"/>
       <c r="M23" s="4" t="inlineStr"/>
@@ -1939,7 +2019,11 @@
           <t>Dirty-tracking + validation</t>
         </is>
       </c>
-      <c r="J24" s="3" t="inlineStr"/>
+      <c r="J24" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K24" s="4" t="inlineStr"/>
       <c r="L24" s="3" t="inlineStr"/>
       <c r="M24" s="4" t="inlineStr"/>
@@ -1991,7 +2075,11 @@
           <t>Intentionally non-editable</t>
         </is>
       </c>
-      <c r="J25" s="3" t="inlineStr"/>
+      <c r="J25" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K25" s="4" t="inlineStr"/>
       <c r="L25" s="3" t="inlineStr"/>
       <c r="M25" s="4" t="inlineStr"/>
@@ -2043,7 +2131,11 @@
           <t>Full upload→persist→refresh</t>
         </is>
       </c>
-      <c r="J26" s="3" t="inlineStr"/>
+      <c r="J26" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K26" s="4" t="inlineStr"/>
       <c r="L26" s="3" t="inlineStr"/>
       <c r="M26" s="4" t="inlineStr"/>
@@ -2095,7 +2187,11 @@
           <t>Preset persistence</t>
         </is>
       </c>
-      <c r="J27" s="3" t="inlineStr"/>
+      <c r="J27" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K27" s="4" t="inlineStr"/>
       <c r="L27" s="3" t="inlineStr"/>
       <c r="M27" s="4" t="inlineStr"/>
@@ -2147,7 +2243,11 @@
           <t>Current-password re-verification</t>
         </is>
       </c>
-      <c r="J28" s="3" t="inlineStr"/>
+      <c r="J28" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K28" s="4" t="inlineStr"/>
       <c r="L28" s="3" t="inlineStr"/>
       <c r="M28" s="4" t="inlineStr"/>
@@ -2199,7 +2299,11 @@
           <t>Client-side export of 4 tables</t>
         </is>
       </c>
-      <c r="J29" s="3" t="inlineStr"/>
+      <c r="J29" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K29" s="4" t="inlineStr"/>
       <c r="L29" s="3" t="inlineStr"/>
       <c r="M29" s="4" t="inlineStr"/>
@@ -2323,7 +2427,11 @@
           <t>Persisted + graceful fallback</t>
         </is>
       </c>
-      <c r="J31" s="3" t="inlineStr"/>
+      <c r="J31" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K31" s="4" t="inlineStr"/>
       <c r="L31" s="3" t="inlineStr"/>
       <c r="M31" s="4" t="inlineStr"/>
@@ -2375,7 +2483,11 @@
           <t>Pending-vs-saved diff</t>
         </is>
       </c>
-      <c r="J32" s="3" t="inlineStr"/>
+      <c r="J32" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K32" s="4" t="inlineStr"/>
       <c r="L32" s="3" t="inlineStr"/>
       <c r="M32" s="4" t="inlineStr"/>
@@ -2427,9 +2539,21 @@
           <t>Behavior in UniversityEmailLink (see ONB-07); only placement confirmed here</t>
         </is>
       </c>
-      <c r="J33" s="3" t="inlineStr"/>
-      <c r="K33" s="4" t="inlineStr"/>
-      <c r="L33" s="3" t="inlineStr"/>
+      <c r="J33" s="21" t="inlineStr">
+        <is>
+          <t>PASS (relocated)</t>
+        </is>
+      </c>
+      <c r="K33" s="4" t="inlineStr">
+        <is>
+          <t>Key-file citation Settings.tsx:383 is stale — &lt;UniversityEmailLink/&gt; is no longer rendered in Settings.tsx at all; it's now used in src/pages/Ascent.tsx and src/pages/Onboarding.tsx. University-email linking is still reachable, just moved off the Settings page as part of the Academic Fingerprint/Ascent work.</t>
+        </is>
+      </c>
+      <c r="L33" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="M33" s="4" t="inlineStr"/>
       <c r="N33" s="4" t="inlineStr"/>
     </row>
@@ -2479,9 +2603,21 @@
           <t>Delegated to AcademicProfileEditor (see ONB-10)</t>
         </is>
       </c>
-      <c r="J34" s="3" t="inlineStr"/>
-      <c r="K34" s="4" t="inlineStr"/>
-      <c r="L34" s="3" t="inlineStr"/>
+      <c r="J34" s="21" t="inlineStr">
+        <is>
+          <t>PASS (relocated)</t>
+        </is>
+      </c>
+      <c r="K34" s="4" t="inlineStr">
+        <is>
+          <t>Same relocation as AUTH-32 — &lt;AcademicProfileEditor/&gt; now renders in Ascent.tsx/Onboarding.tsx, not Settings.tsx.</t>
+        </is>
+      </c>
+      <c r="L34" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="M34" s="4" t="inlineStr"/>
       <c r="N34" s="4" t="inlineStr"/>
     </row>
@@ -2603,7 +2739,11 @@
           <t>Public i18n static content</t>
         </is>
       </c>
-      <c r="J36" s="3" t="inlineStr"/>
+      <c r="J36" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K36" s="4" t="inlineStr"/>
       <c r="L36" s="3" t="inlineStr"/>
       <c r="M36" s="4" t="inlineStr"/>
@@ -2655,7 +2795,11 @@
           <t>Public i18n</t>
         </is>
       </c>
-      <c r="J37" s="3" t="inlineStr"/>
+      <c r="J37" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K37" s="4" t="inlineStr"/>
       <c r="L37" s="3" t="inlineStr"/>
       <c r="M37" s="4" t="inlineStr"/>
@@ -2707,7 +2851,11 @@
           <t>CTAs wired to /auth</t>
         </is>
       </c>
-      <c r="J38" s="3" t="inlineStr"/>
+      <c r="J38" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K38" s="4" t="inlineStr"/>
       <c r="L38" s="3" t="inlineStr"/>
       <c r="M38" s="4" t="inlineStr"/>
@@ -2831,7 +2979,11 @@
           <t>Catch-all + finally reset</t>
         </is>
       </c>
-      <c r="J40" s="3" t="inlineStr"/>
+      <c r="J40" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K40" s="4" t="inlineStr"/>
       <c r="L40" s="3" t="inlineStr"/>
       <c r="M40" s="4" t="inlineStr"/>
@@ -3019,7 +3171,11 @@
           <t>Server-authoritative model</t>
         </is>
       </c>
-      <c r="J43" s="3" t="inlineStr"/>
+      <c r="J43" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K43" s="4" t="inlineStr"/>
       <c r="L43" s="3" t="inlineStr"/>
       <c r="M43" s="4" t="inlineStr"/>
@@ -3215,7 +3371,11 @@
           <t>complete-gated stepper</t>
         </is>
       </c>
-      <c r="J46" s="3" t="inlineStr"/>
+      <c r="J46" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K46" s="4" t="inlineStr"/>
       <c r="L46" s="3" t="inlineStr"/>
       <c r="M46" s="4" t="inlineStr"/>
@@ -3267,7 +3427,11 @@
           <t>10-min cap</t>
         </is>
       </c>
-      <c r="J47" s="3" t="inlineStr"/>
+      <c r="J47" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K47" s="4" t="inlineStr"/>
       <c r="L47" s="3" t="inlineStr"/>
       <c r="M47" s="4" t="inlineStr"/>
@@ -3383,7 +3547,11 @@
           <t>Distinct from duplicate check</t>
         </is>
       </c>
-      <c r="J49" s="3" t="inlineStr"/>
+      <c r="J49" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K49" s="4" t="inlineStr"/>
       <c r="L49" s="3" t="inlineStr"/>
       <c r="M49" s="4" t="inlineStr"/>
@@ -3507,7 +3675,11 @@
           <t>Run-level idempotency</t>
         </is>
       </c>
-      <c r="J51" s="3" t="inlineStr"/>
+      <c r="J51" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K51" s="4" t="inlineStr"/>
       <c r="L51" s="3" t="inlineStr"/>
       <c r="M51" s="4" t="inlineStr"/>
@@ -3559,7 +3731,11 @@
           <t>25-char threshold routes vision</t>
         </is>
       </c>
-      <c r="J52" s="3" t="inlineStr"/>
+      <c r="J52" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K52" s="4" t="inlineStr"/>
       <c r="L52" s="3" t="inlineStr"/>
       <c r="M52" s="4" t="inlineStr"/>
@@ -3611,7 +3787,11 @@
           <t>Graceful degrade to fallback dict</t>
         </is>
       </c>
-      <c r="J53" s="3" t="inlineStr"/>
+      <c r="J53" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K53" s="4" t="inlineStr"/>
       <c r="L53" s="3" t="inlineStr"/>
       <c r="M53" s="4" t="inlineStr"/>
@@ -3727,7 +3907,11 @@
           <t>No per-slide quiz from v5 parse</t>
         </is>
       </c>
-      <c r="J55" s="3" t="inlineStr"/>
+      <c r="J55" s="26" t="inlineStr">
+        <is>
+          <t>N/A (by design)</t>
+        </is>
+      </c>
       <c r="K55" s="4" t="inlineStr"/>
       <c r="L55" s="3" t="inlineStr"/>
       <c r="M55" s="21" t="inlineStr">
@@ -3787,7 +3971,11 @@
           <t>Suggestions lost on v5 save path</t>
         </is>
       </c>
-      <c r="J56" s="3" t="inlineStr"/>
+      <c r="J56" s="26" t="inlineStr">
+        <is>
+          <t>N/A (known gap)</t>
+        </is>
+      </c>
       <c r="K56" s="4" t="inlineStr"/>
       <c r="L56" s="3" t="inlineStr"/>
       <c r="M56" s="21" t="inlineStr">
@@ -3847,7 +4035,11 @@
           <t>Fire-and-forget embeddings</t>
         </is>
       </c>
-      <c r="J57" s="3" t="inlineStr"/>
+      <c r="J57" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K57" s="4" t="inlineStr"/>
       <c r="L57" s="3" t="inlineStr"/>
       <c r="M57" s="4" t="inlineStr"/>
@@ -3899,7 +4091,11 @@
           <t>Partial slides persisted in v5</t>
         </is>
       </c>
-      <c r="J58" s="3" t="inlineStr"/>
+      <c r="J58" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K58" s="4" t="inlineStr"/>
       <c r="L58" s="3" t="inlineStr"/>
       <c r="M58" s="4" t="inlineStr"/>
@@ -3951,7 +4147,11 @@
           <t>Two distinct save paths</t>
         </is>
       </c>
-      <c r="J59" s="3" t="inlineStr"/>
+      <c r="J59" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K59" s="4" t="inlineStr"/>
       <c r="L59" s="3" t="inlineStr"/>
       <c r="M59" s="4" t="inlineStr"/>
@@ -4003,9 +4203,21 @@
           <t>Full CRUD on slides/quizzes</t>
         </is>
       </c>
-      <c r="J60" s="3" t="inlineStr"/>
-      <c r="K60" s="4" t="inlineStr"/>
-      <c r="L60" s="3" t="inlineStr"/>
+      <c r="J60" s="21" t="inlineStr">
+        <is>
+          <t>PASS (relocated)</t>
+        </is>
+      </c>
+      <c r="K60" s="4" t="inlineStr">
+        <is>
+          <t>Key-file citation src/pages/LectureEdit.tsx no longer exists on main. Edit functionality was ported into src/pages/LectureUpload.tsx (isEditMode flag; code comment at line 432 explicitly says 'ported from legacy LectureEdit'). Slide title/content/summary/quiz editing + save is live at that file, just under a different page/route.</t>
+        </is>
+      </c>
+      <c r="L60" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="M60" s="4" t="inlineStr"/>
       <c r="N60" s="4" t="inlineStr"/>
     </row>
@@ -4055,9 +4267,21 @@
           <t>Per-slide + deck regen</t>
         </is>
       </c>
-      <c r="J61" s="3" t="inlineStr"/>
-      <c r="K61" s="4" t="inlineStr"/>
-      <c r="L61" s="3" t="inlineStr"/>
+      <c r="J61" s="21" t="inlineStr">
+        <is>
+          <t>PASS (relocated)</t>
+        </is>
+      </c>
+      <c r="K61" s="4" t="inlineStr">
+        <is>
+          <t>Same relocation as PDF-20 — the per-slide AI generation calls live in LectureUpload.tsx isEditMode branch now, not a standalone LectureEdit.tsx.</t>
+        </is>
+      </c>
+      <c r="L61" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="M61" s="4" t="inlineStr"/>
       <c r="N61" s="4" t="inlineStr"/>
     </row>
@@ -4107,9 +4331,21 @@
           <t>Separate from main pipeline</t>
         </is>
       </c>
-      <c r="J62" s="3" t="inlineStr"/>
-      <c r="K62" s="4" t="inlineStr"/>
-      <c r="L62" s="3" t="inlineStr"/>
+      <c r="J62" s="4" t="inlineStr">
+        <is>
+          <t>RETIRED (confirmed)</t>
+        </is>
+      </c>
+      <c r="K62" s="4" t="inlineStr">
+        <is>
+          <t>backend/api/v1/fast_upload.py no longer exists — moved to backend/_legacy/fast_upload.py, and it is NOT imported/mounted by backend/main.py or any v1 router (grep confirms zero non-legacy references). src/pages/FastUpload.tsx doesn't exist either, and App.tsx has no route to it. The standalone drop-and-poll Fast Upload flow is fully retired/unreachable, superseded by the regular upload.py + LectureUpload.tsx pipeline. Phase-1 'Functioning' status for this story is stale — the feature existed at that snapshot but has since been archived.</t>
+        </is>
+      </c>
+      <c r="L62" s="4" t="inlineStr">
+        <is>
+          <t>Info — audit correction, not a defect</t>
+        </is>
+      </c>
       <c r="M62" s="4" t="inlineStr"/>
       <c r="N62" s="4" t="inlineStr"/>
     </row>
@@ -4231,9 +4467,21 @@
           <t>Drops bad answers (ported in merge)</t>
         </is>
       </c>
-      <c r="J64" s="3" t="inlineStr"/>
-      <c r="K64" s="4" t="inlineStr"/>
-      <c r="L64" s="3" t="inlineStr"/>
+      <c r="J64" s="4" t="inlineStr">
+        <is>
+          <t>RETIRED (confirmed)</t>
+        </is>
+      </c>
+      <c r="K64" s="4" t="inlineStr">
+        <is>
+          <t>Same root cause as PDF-22 — fast_upload.py's quiz-answer-key logic is archived, unreachable code.</t>
+        </is>
+      </c>
+      <c r="L64" s="4" t="inlineStr">
+        <is>
+          <t>Info — audit correction, not a defect</t>
+        </is>
+      </c>
       <c r="M64" s="4" t="inlineStr"/>
       <c r="N64" s="4" t="inlineStr"/>
     </row>
@@ -4283,9 +4531,21 @@
           <t>Strong task refs</t>
         </is>
       </c>
-      <c r="J65" s="3" t="inlineStr"/>
-      <c r="K65" s="4" t="inlineStr"/>
-      <c r="L65" s="3" t="inlineStr"/>
+      <c r="J65" s="4" t="inlineStr">
+        <is>
+          <t>RETIRED (confirmed)</t>
+        </is>
+      </c>
+      <c r="K65" s="4" t="inlineStr">
+        <is>
+          <t>Same root cause as PDF-22 — the background-task GC/crash-logging guard lives in archived, unmounted code.</t>
+        </is>
+      </c>
+      <c r="L65" s="4" t="inlineStr">
+        <is>
+          <t>Info — audit correction, not a defect</t>
+        </is>
+      </c>
       <c r="M65" s="4" t="inlineStr"/>
       <c r="N65" s="4" t="inlineStr"/>
     </row>
@@ -4335,7 +4595,11 @@
           <t>Dev inspector UI</t>
         </is>
       </c>
-      <c r="J66" s="3" t="inlineStr"/>
+      <c r="J66" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K66" s="4" t="inlineStr"/>
       <c r="L66" s="3" t="inlineStr"/>
       <c r="M66" s="4" t="inlineStr"/>
@@ -4459,7 +4723,11 @@
           <t>No-AI extraction view</t>
         </is>
       </c>
-      <c r="J68" s="3" t="inlineStr"/>
+      <c r="J68" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K68" s="4" t="inlineStr"/>
       <c r="L68" s="3" t="inlineStr"/>
       <c r="M68" s="4" t="inlineStr"/>
@@ -4583,7 +4851,11 @@
           <t>Alternate lazy mode</t>
         </is>
       </c>
-      <c r="J70" s="3" t="inlineStr"/>
+      <c r="J70" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K70" s="4" t="inlineStr"/>
       <c r="L70" s="3" t="inlineStr"/>
       <c r="M70" s="4" t="inlineStr"/>
@@ -4635,7 +4907,11 @@
           <t>Ownership-checked</t>
         </is>
       </c>
-      <c r="J71" s="3" t="inlineStr"/>
+      <c r="J71" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K71" s="4" t="inlineStr"/>
       <c r="L71" s="3" t="inlineStr"/>
       <c r="M71" s="4" t="inlineStr"/>
@@ -4687,9 +4963,21 @@
           <t>Leftover debug scripts — candidate for removal</t>
         </is>
       </c>
-      <c r="J72" s="3" t="inlineStr"/>
-      <c r="K72" s="4" t="inlineStr"/>
-      <c r="L72" s="3" t="inlineStr"/>
+      <c r="J72" s="21" t="inlineStr">
+        <is>
+          <t>PASS (resolved)</t>
+        </is>
+      </c>
+      <c r="K72" s="4" t="inlineStr">
+        <is>
+          <t>backend/test_auth.py and backend/test_auth2.py (the ad-hoc untracked debug scripts flagged in Phase 1) no longer exist in the working tree or git status — housekeeping already done.</t>
+        </is>
+      </c>
+      <c r="L72" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="M72" s="4" t="inlineStr"/>
       <c r="N72" s="4" t="inlineStr"/>
     </row>
@@ -4803,7 +5091,11 @@
           <t>Ownership-checked update</t>
         </is>
       </c>
-      <c r="J74" s="3" t="inlineStr"/>
+      <c r="J74" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K74" s="4" t="inlineStr"/>
       <c r="L74" s="3" t="inlineStr"/>
       <c r="M74" s="4" t="inlineStr"/>
@@ -4855,7 +5147,11 @@
           <t>Endpoint + gating</t>
         </is>
       </c>
-      <c r="J75" s="3" t="inlineStr"/>
+      <c r="J75" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K75" s="4" t="inlineStr"/>
       <c r="L75" s="3" t="inlineStr"/>
       <c r="M75" s="4" t="inlineStr"/>
@@ -4907,7 +5203,11 @@
           <t>UI gate + backend 409/reassign</t>
         </is>
       </c>
-      <c r="J76" s="3" t="inlineStr"/>
+      <c r="J76" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K76" s="4" t="inlineStr"/>
       <c r="L76" s="3" t="inlineStr"/>
       <c r="M76" s="4" t="inlineStr"/>
@@ -4959,7 +5259,11 @@
           <t>Archive flag flow</t>
         </is>
       </c>
-      <c r="J77" s="3" t="inlineStr"/>
+      <c r="J77" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K77" s="4" t="inlineStr"/>
       <c r="L77" s="3" t="inlineStr"/>
       <c r="M77" s="4" t="inlineStr"/>
@@ -5011,7 +5315,11 @@
           <t>Role-aware list</t>
         </is>
       </c>
-      <c r="J78" s="3" t="inlineStr"/>
+      <c r="J78" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K78" s="4" t="inlineStr"/>
       <c r="L78" s="3" t="inlineStr"/>
       <c r="M78" s="4" t="inlineStr"/>
@@ -5063,7 +5371,11 @@
           <t>Owner sees full roster</t>
         </is>
       </c>
-      <c r="J79" s="3" t="inlineStr"/>
+      <c r="J79" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K79" s="4" t="inlineStr"/>
       <c r="L79" s="3" t="inlineStr"/>
       <c r="M79" s="4" t="inlineStr"/>
@@ -5115,7 +5427,11 @@
           <t>Ownership-checked assign</t>
         </is>
       </c>
-      <c r="J80" s="3" t="inlineStr"/>
+      <c r="J80" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K80" s="4" t="inlineStr"/>
       <c r="L80" s="3" t="inlineStr"/>
       <c r="M80" s="4" t="inlineStr"/>
@@ -5167,7 +5483,11 @@
           <t>courseId prefill</t>
         </is>
       </c>
-      <c r="J81" s="3" t="inlineStr"/>
+      <c r="J81" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K81" s="4" t="inlineStr"/>
       <c r="L81" s="3" t="inlineStr"/>
       <c r="M81" s="4" t="inlineStr"/>
@@ -5219,7 +5539,11 @@
           <t>Unassign + archive combined</t>
         </is>
       </c>
-      <c r="J82" s="3" t="inlineStr"/>
+      <c r="J82" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K82" s="4" t="inlineStr"/>
       <c r="L82" s="3" t="inlineStr"/>
       <c r="M82" s="4" t="inlineStr"/>
@@ -5271,7 +5595,11 @@
           <t>Archived listing + search</t>
         </is>
       </c>
-      <c r="J83" s="3" t="inlineStr"/>
+      <c r="J83" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K83" s="4" t="inlineStr"/>
       <c r="L83" s="3" t="inlineStr"/>
       <c r="M83" s="4" t="inlineStr"/>
@@ -5323,7 +5651,11 @@
           <t>Restore via PATCH</t>
         </is>
       </c>
-      <c r="J84" s="3" t="inlineStr"/>
+      <c r="J84" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K84" s="4" t="inlineStr"/>
       <c r="L84" s="3" t="inlineStr"/>
       <c r="M84" s="4" t="inlineStr"/>
@@ -5375,7 +5707,11 @@
           <t>Guarded purge</t>
         </is>
       </c>
-      <c r="J85" s="3" t="inlineStr"/>
+      <c r="J85" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K85" s="4" t="inlineStr"/>
       <c r="L85" s="3" t="inlineStr"/>
       <c r="M85" s="4" t="inlineStr"/>
@@ -5427,7 +5763,11 @@
           <t>Lecture archive ops</t>
         </is>
       </c>
-      <c r="J86" s="3" t="inlineStr"/>
+      <c r="J86" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K86" s="4" t="inlineStr"/>
       <c r="L86" s="3" t="inlineStr"/>
       <c r="M86" s="4" t="inlineStr"/>
@@ -5479,7 +5819,11 @@
           <t>Open catalog browse</t>
         </is>
       </c>
-      <c r="J87" s="3" t="inlineStr"/>
+      <c r="J87" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K87" s="4" t="inlineStr"/>
       <c r="L87" s="3" t="inlineStr"/>
       <c r="M87" s="4" t="inlineStr"/>
@@ -5531,7 +5875,11 @@
           <t>RPC-backed recs</t>
         </is>
       </c>
-      <c r="J88" s="3" t="inlineStr"/>
+      <c r="J88" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K88" s="4" t="inlineStr"/>
       <c r="L88" s="3" t="inlineStr"/>
       <c r="M88" s="4" t="inlineStr"/>
@@ -5583,7 +5931,11 @@
           <t>Idempotent enroll</t>
         </is>
       </c>
-      <c r="J89" s="3" t="inlineStr"/>
+      <c r="J89" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K89" s="4" t="inlineStr"/>
       <c r="L89" s="3" t="inlineStr"/>
       <c r="M89" s="4" t="inlineStr"/>
@@ -5635,7 +5987,11 @@
           <t>Endpoint exists, no UI</t>
         </is>
       </c>
-      <c r="J90" s="3" t="inlineStr"/>
+      <c r="J90" s="26" t="inlineStr">
+        <is>
+          <t>N/A (feature gap)</t>
+        </is>
+      </c>
       <c r="K90" s="4" t="inlineStr"/>
       <c r="L90" s="3" t="inlineStr"/>
       <c r="M90" s="21" t="inlineStr">
@@ -5759,7 +6115,11 @@
           <t>Library renders/navigates</t>
         </is>
       </c>
-      <c r="J92" s="3" t="inlineStr"/>
+      <c r="J92" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K92" s="4" t="inlineStr"/>
       <c r="L92" s="3" t="inlineStr"/>
       <c r="M92" s="4" t="inlineStr"/>
@@ -5811,9 +6171,21 @@
           <t>Client reads tables directly; 'Enrolled' badge may not reflect course_enrollments</t>
         </is>
       </c>
-      <c r="J93" s="3" t="inlineStr"/>
-      <c r="K93" s="4" t="inlineStr"/>
-      <c r="L93" s="3" t="inlineStr"/>
+      <c r="J93" s="4" t="inlineStr">
+        <is>
+          <t>Partial (confirmed)</t>
+        </is>
+      </c>
+      <c r="K93" s="4" t="inlineStr">
+        <is>
+          <t>useStudentDashboard.ts:54-60 confirmed: coursesQuery/lecturesQuery call fetchStudentCourses/fetchStudentLectures directly against Supabase tables, not the enrollment-aware /api/courses endpoint. Visibility is RLS-governed, not course_enrollments-governed, so an 'Enrolled' badge in the UI may not reflect true enrollment state. Confirmed still true on current main; no product decision made yet.</t>
+        </is>
+      </c>
+      <c r="L93" s="4" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
       <c r="M93" s="4" t="inlineStr"/>
       <c r="N93" s="4" t="inlineStr"/>
     </row>
@@ -5863,7 +6235,11 @@
           <t>Legacy timeline view</t>
         </is>
       </c>
-      <c r="J94" s="3" t="inlineStr"/>
+      <c r="J94" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K94" s="4" t="inlineStr"/>
       <c r="L94" s="3" t="inlineStr"/>
       <c r="M94" s="4" t="inlineStr"/>
@@ -5987,7 +6363,11 @@
           <t>Inline + full-page open</t>
         </is>
       </c>
-      <c r="J96" s="3" t="inlineStr"/>
+      <c r="J96" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K96" s="4" t="inlineStr"/>
       <c r="L96" s="3" t="inlineStr"/>
       <c r="M96" s="4" t="inlineStr"/>
@@ -6039,7 +6419,11 @@
           <t>localStorage recency</t>
         </is>
       </c>
-      <c r="J97" s="3" t="inlineStr"/>
+      <c r="J97" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K97" s="4" t="inlineStr"/>
       <c r="L97" s="3" t="inlineStr"/>
       <c r="M97" s="4" t="inlineStr"/>
@@ -6091,7 +6475,11 @@
           <t>Slug→id fallback</t>
         </is>
       </c>
-      <c r="J98" s="3" t="inlineStr"/>
+      <c r="J98" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K98" s="4" t="inlineStr"/>
       <c r="L98" s="3" t="inlineStr"/>
       <c r="M98" s="4" t="inlineStr"/>
@@ -6215,7 +6603,11 @@
           <t>Count rules differ by context (intentional)</t>
         </is>
       </c>
-      <c r="J100" s="3" t="inlineStr"/>
+      <c r="J100" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K100" s="4" t="inlineStr"/>
       <c r="L100" s="3" t="inlineStr"/>
       <c r="M100" s="4" t="inlineStr"/>
@@ -6339,7 +6731,11 @@
           <t>If GEMINI_API_KEY unset, embeddings return zero vector → retrieval degrades to current-slide-only</t>
         </is>
       </c>
-      <c r="J102" s="3" t="inlineStr"/>
+      <c r="J102" s="26" t="inlineStr">
+        <is>
+          <t>N/A (config)</t>
+        </is>
+      </c>
       <c r="K102" s="4" t="inlineStr"/>
       <c r="L102" s="3" t="inlineStr"/>
       <c r="M102" s="21" t="inlineStr">
@@ -6399,7 +6795,11 @@
           <t>Prompt-instructed (not enforced)</t>
         </is>
       </c>
-      <c r="J103" s="3" t="inlineStr"/>
+      <c r="J103" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K103" s="4" t="inlineStr"/>
       <c r="L103" s="3" t="inlineStr"/>
       <c r="M103" s="4" t="inlineStr"/>
@@ -6515,7 +6915,11 @@
           <t>Neutralize-not-block</t>
         </is>
       </c>
-      <c r="J105" s="3" t="inlineStr"/>
+      <c r="J105" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K105" s="4" t="inlineStr"/>
       <c r="L105" s="3" t="inlineStr"/>
       <c r="M105" s="4" t="inlineStr"/>
@@ -6567,7 +6971,11 @@
           <t>Ownership + lecture-auth checks; LectureChat doesn't pass session_id</t>
         </is>
       </c>
-      <c r="J106" s="3" t="inlineStr"/>
+      <c r="J106" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K106" s="4" t="inlineStr"/>
       <c r="L106" s="3" t="inlineStr"/>
       <c r="M106" s="4" t="inlineStr"/>
@@ -6619,7 +7027,11 @@
           <t>Multiple fallback layers</t>
         </is>
       </c>
-      <c r="J107" s="3" t="inlineStr"/>
+      <c r="J107" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K107" s="4" t="inlineStr"/>
       <c r="L107" s="3" t="inlineStr"/>
       <c r="M107" s="4" t="inlineStr"/>
@@ -6743,7 +7155,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="J109" s="3" t="inlineStr"/>
+      <c r="J109" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K109" s="4" t="inlineStr"/>
       <c r="L109" s="3" t="inlineStr"/>
       <c r="M109" s="4" t="inlineStr"/>
@@ -6795,7 +7211,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="J110" s="3" t="inlineStr"/>
+      <c r="J110" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K110" s="4" t="inlineStr"/>
       <c r="L110" s="3" t="inlineStr"/>
       <c r="M110" s="4" t="inlineStr"/>
@@ -6847,7 +7267,11 @@
           <t>Requires ≥2 valid linked slides else dropped</t>
         </is>
       </c>
-      <c r="J111" s="3" t="inlineStr"/>
+      <c r="J111" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K111" s="4" t="inlineStr"/>
       <c r="L111" s="3" t="inlineStr"/>
       <c r="M111" s="4" t="inlineStr"/>
@@ -6899,7 +7323,11 @@
           <t>In-process per-worker cache (512 cap)</t>
         </is>
       </c>
-      <c r="J112" s="3" t="inlineStr"/>
+      <c r="J112" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K112" s="4" t="inlineStr"/>
       <c r="L112" s="3" t="inlineStr"/>
       <c r="M112" s="4" t="inlineStr"/>
@@ -7079,7 +7507,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="J115" s="3" t="inlineStr"/>
+      <c r="J115" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K115" s="4" t="inlineStr"/>
       <c r="L115" s="3" t="inlineStr"/>
       <c r="M115" s="4" t="inlineStr"/>
@@ -7131,7 +7563,11 @@
           <t>SSRF-guarded; uses HTTP/2 wrapper (ported in merge)</t>
         </is>
       </c>
-      <c r="J116" s="3" t="inlineStr"/>
+      <c r="J116" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K116" s="4" t="inlineStr"/>
       <c r="L116" s="3" t="inlineStr"/>
       <c r="M116" s="4" t="inlineStr"/>
@@ -7183,7 +7619,11 @@
           <t>Unrepairable items dropped</t>
         </is>
       </c>
-      <c r="J117" s="3" t="inlineStr"/>
+      <c r="J117" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K117" s="4" t="inlineStr"/>
       <c r="L117" s="3" t="inlineStr"/>
       <c r="M117" s="4" t="inlineStr"/>
@@ -7235,7 +7675,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="J118" s="3" t="inlineStr"/>
+      <c r="J118" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K118" s="4" t="inlineStr"/>
       <c r="L118" s="3" t="inlineStr"/>
       <c r="M118" s="4" t="inlineStr"/>
@@ -7287,9 +7731,21 @@
           <t>Endpoint exists; no frontend caller found</t>
         </is>
       </c>
-      <c r="J119" s="3" t="inlineStr"/>
-      <c r="K119" s="4" t="inlineStr"/>
-      <c r="L119" s="3" t="inlineStr"/>
+      <c r="J119" s="21" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K119" s="4" t="inlineStr">
+        <is>
+          <t>Phase-1 evidence said 'no frontend caller found' — incorrect/incomplete scan. useTTS() (src/hooks/useTTS.ts:92, POSTs /api/v1/ai/tts) is actually called from InlineLecturePlayer.tsx, QuizCard.tsx, and SlideViewer.tsx. TTS is wired end-to-end.</t>
+        </is>
+      </c>
+      <c r="L119" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="M119" s="4" t="inlineStr"/>
       <c r="N119" s="4" t="inlineStr"/>
     </row>
@@ -7483,7 +7939,11 @@
           <t>GET + useQuery wired</t>
         </is>
       </c>
-      <c r="J122" s="3" t="inlineStr"/>
+      <c r="J122" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K122" s="4" t="inlineStr"/>
       <c r="L122" s="3" t="inlineStr"/>
       <c r="M122" s="4" t="inlineStr"/>
@@ -7599,7 +8059,11 @@
           <t>Role-gated button + backend dep</t>
         </is>
       </c>
-      <c r="J124" s="3" t="inlineStr"/>
+      <c r="J124" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K124" s="4" t="inlineStr"/>
       <c r="L124" s="3" t="inlineStr"/>
       <c r="M124" s="4" t="inlineStr"/>
@@ -7651,7 +8115,11 @@
           <t>Explicit status mapping</t>
         </is>
       </c>
-      <c r="J125" s="3" t="inlineStr"/>
+      <c r="J125" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K125" s="4" t="inlineStr"/>
       <c r="L125" s="3" t="inlineStr"/>
       <c r="M125" s="4" t="inlineStr"/>
@@ -7703,7 +8171,11 @@
           <t>Embedding-based ingest + auto-trigger</t>
         </is>
       </c>
-      <c r="J126" s="3" t="inlineStr"/>
+      <c r="J126" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K126" s="4" t="inlineStr"/>
       <c r="L126" s="3" t="inlineStr"/>
       <c r="M126" s="4" t="inlineStr"/>
@@ -7755,7 +8227,11 @@
           <t>Mastery RPC + card</t>
         </is>
       </c>
-      <c r="J127" s="3" t="inlineStr"/>
+      <c r="J127" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K127" s="4" t="inlineStr"/>
       <c r="L127" s="3" t="inlineStr"/>
       <c r="M127" s="4" t="inlineStr"/>
@@ -7807,7 +8283,11 @@
           <t>Access-checked concept list</t>
         </is>
       </c>
-      <c r="J128" s="3" t="inlineStr"/>
+      <c r="J128" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K128" s="4" t="inlineStr"/>
       <c r="L128" s="3" t="inlineStr"/>
       <c r="M128" s="4" t="inlineStr"/>
@@ -7859,7 +8339,11 @@
           <t>Result + accessibility filter</t>
         </is>
       </c>
-      <c r="J129" s="3" t="inlineStr"/>
+      <c r="J129" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K129" s="4" t="inlineStr"/>
       <c r="L129" s="3" t="inlineStr"/>
       <c r="M129" s="4" t="inlineStr"/>
@@ -7911,7 +8395,11 @@
           <t>Access-gated list</t>
         </is>
       </c>
-      <c r="J130" s="3" t="inlineStr"/>
+      <c r="J130" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K130" s="4" t="inlineStr"/>
       <c r="L130" s="3" t="inlineStr"/>
       <c r="M130" s="4" t="inlineStr"/>
@@ -7963,7 +8451,11 @@
           <t>MIME+size guard, transactional</t>
         </is>
       </c>
-      <c r="J131" s="3" t="inlineStr"/>
+      <c r="J131" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K131" s="4" t="inlineStr"/>
       <c r="L131" s="3" t="inlineStr"/>
       <c r="M131" s="4" t="inlineStr"/>
@@ -8015,7 +8507,11 @@
           <t>Owner-checked</t>
         </is>
       </c>
-      <c r="J132" s="3" t="inlineStr"/>
+      <c r="J132" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K132" s="4" t="inlineStr"/>
       <c r="L132" s="3" t="inlineStr"/>
       <c r="M132" s="4" t="inlineStr"/>
@@ -8067,7 +8563,11 @@
           <t>Owner-checked</t>
         </is>
       </c>
-      <c r="J133" s="3" t="inlineStr"/>
+      <c r="J133" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K133" s="4" t="inlineStr"/>
       <c r="L133" s="3" t="inlineStr"/>
       <c r="M133" s="4" t="inlineStr"/>
@@ -8119,7 +8619,11 @@
           <t>Signed URL + access gate</t>
         </is>
       </c>
-      <c r="J134" s="3" t="inlineStr"/>
+      <c r="J134" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K134" s="4" t="inlineStr"/>
       <c r="L134" s="3" t="inlineStr"/>
       <c r="M134" s="4" t="inlineStr"/>
@@ -8171,7 +8675,11 @@
           <t>Role-aware filtering</t>
         </is>
       </c>
-      <c r="J135" s="3" t="inlineStr"/>
+      <c r="J135" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K135" s="4" t="inlineStr"/>
       <c r="L135" s="3" t="inlineStr"/>
       <c r="M135" s="4" t="inlineStr"/>
@@ -8223,7 +8731,11 @@
           <t>Owner-checked</t>
         </is>
       </c>
-      <c r="J136" s="3" t="inlineStr"/>
+      <c r="J136" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K136" s="4" t="inlineStr"/>
       <c r="L136" s="3" t="inlineStr"/>
       <c r="M136" s="4" t="inlineStr"/>
@@ -8275,7 +8787,11 @@
           <t>Errors 400 if no quizzes</t>
         </is>
       </c>
-      <c r="J137" s="3" t="inlineStr"/>
+      <c r="J137" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K137" s="4" t="inlineStr"/>
       <c r="L137" s="3" t="inlineStr"/>
       <c r="M137" s="4" t="inlineStr"/>
@@ -8327,7 +8843,11 @@
           <t>Published+access gate</t>
         </is>
       </c>
-      <c r="J138" s="3" t="inlineStr"/>
+      <c r="J138" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K138" s="4" t="inlineStr"/>
       <c r="L138" s="3" t="inlineStr"/>
       <c r="M138" s="4" t="inlineStr"/>
@@ -8379,7 +8899,11 @@
           <t>Creator-checked, enum validated</t>
         </is>
       </c>
-      <c r="J139" s="3" t="inlineStr"/>
+      <c r="J139" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K139" s="4" t="inlineStr"/>
       <c r="L139" s="3" t="inlineStr"/>
       <c r="M139" s="4" t="inlineStr"/>
@@ -8431,7 +8955,11 @@
           <t>Creator-checked</t>
         </is>
       </c>
-      <c r="J140" s="3" t="inlineStr"/>
+      <c r="J140" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K140" s="4" t="inlineStr"/>
       <c r="L140" s="3" t="inlineStr"/>
       <c r="M140" s="4" t="inlineStr"/>
@@ -8483,7 +9011,11 @@
           <t>Manual-only add, reindex on delete</t>
         </is>
       </c>
-      <c r="J141" s="3" t="inlineStr"/>
+      <c r="J141" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K141" s="4" t="inlineStr"/>
       <c r="L141" s="3" t="inlineStr"/>
       <c r="M141" s="4" t="inlineStr"/>
@@ -8535,7 +9067,11 @@
           <t>Creator-checked</t>
         </is>
       </c>
-      <c r="J142" s="3" t="inlineStr"/>
+      <c r="J142" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K142" s="4" t="inlineStr"/>
       <c r="L142" s="3" t="inlineStr"/>
       <c r="M142" s="4" t="inlineStr"/>
@@ -8587,7 +9123,11 @@
           <t>free_form not graded; short_answer exact-match only → all-free_form sheet scores 0.0</t>
         </is>
       </c>
-      <c r="J143" s="3" t="inlineStr"/>
+      <c r="J143" s="26" t="inlineStr">
+        <is>
+          <t>N/A (by design)</t>
+        </is>
+      </c>
       <c r="K143" s="4" t="inlineStr"/>
       <c r="L143" s="3" t="inlineStr"/>
       <c r="M143" s="21" t="inlineStr">
@@ -8647,7 +9187,11 @@
           <t>Server-enforced preview flag</t>
         </is>
       </c>
-      <c r="J144" s="3" t="inlineStr"/>
+      <c r="J144" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K144" s="4" t="inlineStr"/>
       <c r="L144" s="3" t="inlineStr"/>
       <c r="M144" s="4" t="inlineStr"/>
@@ -8699,7 +9243,11 @@
           <t>Own-attempts query</t>
         </is>
       </c>
-      <c r="J145" s="3" t="inlineStr"/>
+      <c r="J145" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K145" s="4" t="inlineStr"/>
       <c r="L145" s="3" t="inlineStr"/>
       <c r="M145" s="4" t="inlineStr"/>
@@ -8751,7 +9299,11 @@
           <t>Role branch + status compute</t>
         </is>
       </c>
-      <c r="J146" s="3" t="inlineStr"/>
+      <c r="J146" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K146" s="4" t="inlineStr"/>
       <c r="L146" s="3" t="inlineStr"/>
       <c r="M146" s="4" t="inlineStr"/>
@@ -8803,7 +9355,11 @@
           <t>404-hiding access gate</t>
         </is>
       </c>
-      <c r="J147" s="3" t="inlineStr"/>
+      <c r="J147" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K147" s="4" t="inlineStr"/>
       <c r="L147" s="3" t="inlineStr"/>
       <c r="M147" s="4" t="inlineStr"/>
@@ -8855,7 +9411,11 @@
           <t>Ownership-verified create</t>
         </is>
       </c>
-      <c r="J148" s="3" t="inlineStr"/>
+      <c r="J148" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K148" s="4" t="inlineStr"/>
       <c r="L148" s="3" t="inlineStr"/>
       <c r="M148" s="4" t="inlineStr"/>
@@ -8907,7 +9467,11 @@
           <t>Owner-checked partial update</t>
         </is>
       </c>
-      <c r="J149" s="3" t="inlineStr"/>
+      <c r="J149" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K149" s="4" t="inlineStr"/>
       <c r="L149" s="3" t="inlineStr"/>
       <c r="M149" s="4" t="inlineStr"/>
@@ -8959,7 +9523,11 @@
           <t>Owner-checked</t>
         </is>
       </c>
-      <c r="J150" s="3" t="inlineStr"/>
+      <c r="J150" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K150" s="4" t="inlineStr"/>
       <c r="L150" s="3" t="inlineStr"/>
       <c r="M150" s="4" t="inlineStr"/>
@@ -9011,7 +9579,11 @@
           <t>Scoped, PII-minimized</t>
         </is>
       </c>
-      <c r="J151" s="3" t="inlineStr"/>
+      <c r="J151" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K151" s="4" t="inlineStr"/>
       <c r="L151" s="3" t="inlineStr"/>
       <c r="M151" s="4" t="inlineStr"/>
@@ -9063,7 +9635,11 @@
           <t>Progress-derived (by design)</t>
         </is>
       </c>
-      <c r="J152" s="3" t="inlineStr"/>
+      <c r="J152" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K152" s="4" t="inlineStr"/>
       <c r="L152" s="3" t="inlineStr"/>
       <c r="M152" s="4" t="inlineStr"/>
@@ -9115,7 +9691,11 @@
           <t>Panel + CTA</t>
         </is>
       </c>
-      <c r="J153" s="3" t="inlineStr"/>
+      <c r="J153" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K153" s="4" t="inlineStr"/>
       <c r="L153" s="3" t="inlineStr"/>
       <c r="M153" s="4" t="inlineStr"/>
@@ -9167,7 +9747,11 @@
           <t>Granular queries + realtime + states</t>
         </is>
       </c>
-      <c r="J154" s="3" t="inlineStr"/>
+      <c r="J154" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K154" s="4" t="inlineStr"/>
       <c r="L154" s="3" t="inlineStr"/>
       <c r="M154" s="4" t="inlineStr"/>
@@ -9219,7 +9803,11 @@
           <t>selectHero + HeroStage + MediaRail</t>
         </is>
       </c>
-      <c r="J155" s="3" t="inlineStr"/>
+      <c r="J155" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K155" s="4" t="inlineStr"/>
       <c r="L155" s="3" t="inlineStr"/>
       <c r="M155" s="4" t="inlineStr"/>
@@ -9271,7 +9859,11 @@
           <t>Widgets from profile+achievements+progress</t>
         </is>
       </c>
-      <c r="J156" s="3" t="inlineStr"/>
+      <c r="J156" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K156" s="4" t="inlineStr"/>
       <c r="L156" s="3" t="inlineStr"/>
       <c r="M156" s="4" t="inlineStr"/>
@@ -9323,7 +9915,11 @@
           <t>Pure derivation</t>
         </is>
       </c>
-      <c r="J157" s="3" t="inlineStr"/>
+      <c r="J157" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K157" s="4" t="inlineStr"/>
       <c r="L157" s="3" t="inlineStr"/>
       <c r="M157" s="4" t="inlineStr"/>
@@ -9375,7 +9971,11 @@
           <t>Wired with dedupe</t>
         </is>
       </c>
-      <c r="J158" s="3" t="inlineStr"/>
+      <c r="J158" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K158" s="4" t="inlineStr"/>
       <c r="L158" s="3" t="inlineStr"/>
       <c r="M158" s="4" t="inlineStr"/>
@@ -9427,7 +10027,11 @@
           <t>buildRows rendered</t>
         </is>
       </c>
-      <c r="J159" s="3" t="inlineStr"/>
+      <c r="J159" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K159" s="4" t="inlineStr"/>
       <c r="L159" s="3" t="inlineStr"/>
       <c r="M159" s="4" t="inlineStr"/>
@@ -9479,7 +10083,11 @@
           <t>Non-blocking writes</t>
         </is>
       </c>
-      <c r="J160" s="3" t="inlineStr"/>
+      <c r="J160" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K160" s="4" t="inlineStr"/>
       <c r="L160" s="3" t="inlineStr"/>
       <c r="M160" s="4" t="inlineStr"/>
@@ -9531,7 +10139,11 @@
           <t>Threshold hardcoded &gt;2</t>
         </is>
       </c>
-      <c r="J161" s="3" t="inlineStr"/>
+      <c r="J161" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K161" s="4" t="inlineStr"/>
       <c r="L161" s="3" t="inlineStr"/>
       <c r="M161" s="4" t="inlineStr"/>
@@ -9583,7 +10195,11 @@
           <t>heroKind branch</t>
         </is>
       </c>
-      <c r="J162" s="3" t="inlineStr"/>
+      <c r="J162" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K162" s="4" t="inlineStr"/>
       <c r="L162" s="3" t="inlineStr"/>
       <c r="M162" s="4" t="inlineStr"/>
@@ -9635,7 +10251,11 @@
           <t>Conditional on continueLectures[0]</t>
         </is>
       </c>
-      <c r="J163" s="3" t="inlineStr"/>
+      <c r="J163" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K163" s="4" t="inlineStr"/>
       <c r="L163" s="3" t="inlineStr"/>
       <c r="M163" s="4" t="inlineStr"/>
@@ -9687,7 +10307,11 @@
           <t>role=button + Enter/Space</t>
         </is>
       </c>
-      <c r="J164" s="3" t="inlineStr"/>
+      <c r="J164" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K164" s="4" t="inlineStr"/>
       <c r="L164" s="3" t="inlineStr"/>
       <c r="M164" s="4" t="inlineStr"/>
@@ -9739,7 +10363,11 @@
           <t>Deferred mount</t>
         </is>
       </c>
-      <c r="J165" s="3" t="inlineStr"/>
+      <c r="J165" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K165" s="4" t="inlineStr"/>
       <c r="L165" s="3" t="inlineStr"/>
       <c r="M165" s="4" t="inlineStr"/>
@@ -9791,7 +10419,11 @@
           <t>Query + defensive sort</t>
         </is>
       </c>
-      <c r="J166" s="3" t="inlineStr"/>
+      <c r="J166" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K166" s="4" t="inlineStr"/>
       <c r="L166" s="3" t="inlineStr"/>
       <c r="M166" s="4" t="inlineStr"/>
@@ -9843,7 +10475,11 @@
           <t>deep_link + per-type fallback</t>
         </is>
       </c>
-      <c r="J167" s="3" t="inlineStr"/>
+      <c r="J167" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K167" s="4" t="inlineStr"/>
       <c r="L167" s="3" t="inlineStr"/>
       <c r="M167" s="4" t="inlineStr"/>
@@ -9895,7 +10531,11 @@
           <t>Per-rule cool-off (streak1/assignment2/review14)</t>
         </is>
       </c>
-      <c r="J168" s="3" t="inlineStr"/>
+      <c r="J168" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K168" s="4" t="inlineStr"/>
       <c r="L168" s="3" t="inlineStr"/>
       <c r="M168" s="4" t="inlineStr"/>
@@ -9947,7 +10587,11 @@
           <t>Boundary-exact</t>
         </is>
       </c>
-      <c r="J169" s="3" t="inlineStr"/>
+      <c r="J169" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K169" s="4" t="inlineStr"/>
       <c r="L169" s="3" t="inlineStr"/>
       <c r="M169" s="4" t="inlineStr"/>
@@ -9999,7 +10643,11 @@
           <t>Status via compute_status_for_user</t>
         </is>
       </c>
-      <c r="J170" s="3" t="inlineStr"/>
+      <c r="J170" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K170" s="4" t="inlineStr"/>
       <c r="L170" s="3" t="inlineStr"/>
       <c r="M170" s="4" t="inlineStr"/>
@@ -10051,7 +10699,11 @@
           <t>Thresholds constants</t>
         </is>
       </c>
-      <c r="J171" s="3" t="inlineStr"/>
+      <c r="J171" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K171" s="4" t="inlineStr"/>
       <c r="L171" s="3" t="inlineStr"/>
       <c r="M171" s="4" t="inlineStr"/>
@@ -10103,7 +10755,11 @@
           <t>Idempotency via (user,rule,subject)</t>
         </is>
       </c>
-      <c r="J172" s="3" t="inlineStr"/>
+      <c r="J172" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K172" s="4" t="inlineStr"/>
       <c r="L172" s="3" t="inlineStr"/>
       <c r="M172" s="4" t="inlineStr"/>
@@ -10155,7 +10811,11 @@
           <t>Disabled by default; no nudges fire unless env flag set</t>
         </is>
       </c>
-      <c r="J173" s="3" t="inlineStr"/>
+      <c r="J173" s="26" t="inlineStr">
+        <is>
+          <t>N/A (config)</t>
+        </is>
+      </c>
       <c r="K173" s="4" t="inlineStr"/>
       <c r="L173" s="3" t="inlineStr"/>
       <c r="M173" s="21" t="inlineStr">
@@ -10215,7 +10875,11 @@
           <t>Shared-secret gate</t>
         </is>
       </c>
-      <c r="J174" s="3" t="inlineStr"/>
+      <c r="J174" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K174" s="4" t="inlineStr"/>
       <c r="L174" s="3" t="inlineStr"/>
       <c r="M174" s="4" t="inlineStr"/>
@@ -10267,7 +10931,11 @@
           <t>Pure build_plan + thin assembly</t>
         </is>
       </c>
-      <c r="J175" s="3" t="inlineStr"/>
+      <c r="J175" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K175" s="4" t="inlineStr"/>
       <c r="L175" s="3" t="inlineStr"/>
       <c r="M175" s="4" t="inlineStr"/>
@@ -10319,7 +10987,11 @@
           <t>Cross-day suppression</t>
         </is>
       </c>
-      <c r="J176" s="3" t="inlineStr"/>
+      <c r="J176" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K176" s="4" t="inlineStr"/>
       <c r="L176" s="3" t="inlineStr"/>
       <c r="M176" s="4" t="inlineStr"/>
@@ -10443,7 +11115,11 @@
           <t>Backend honors it but no UI to set study_minutes_per_day</t>
         </is>
       </c>
-      <c r="J178" s="3" t="inlineStr"/>
+      <c r="J178" s="26" t="inlineStr">
+        <is>
+          <t>N/A (feature gap)</t>
+        </is>
+      </c>
       <c r="K178" s="4" t="inlineStr"/>
       <c r="L178" s="3" t="inlineStr"/>
       <c r="M178" s="21" t="inlineStr">
@@ -10503,7 +11179,11 @@
           <t>File-type + 2MB guards</t>
         </is>
       </c>
-      <c r="J179" s="3" t="inlineStr"/>
+      <c r="J179" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K179" s="4" t="inlineStr"/>
       <c r="L179" s="3" t="inlineStr"/>
       <c r="M179" s="4" t="inlineStr"/>
@@ -10555,7 +11235,11 @@
           <t>Cascade + domain pre-select</t>
         </is>
       </c>
-      <c r="J180" s="3" t="inlineStr"/>
+      <c r="J180" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K180" s="4" t="inlineStr"/>
       <c r="L180" s="3" t="inlineStr"/>
       <c r="M180" s="4" t="inlineStr"/>
@@ -10607,7 +11291,11 @@
           <t>hasCatalog flag drives branch</t>
         </is>
       </c>
-      <c r="J181" s="3" t="inlineStr"/>
+      <c r="J181" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K181" s="4" t="inlineStr"/>
       <c r="L181" s="3" t="inlineStr"/>
       <c r="M181" s="4" t="inlineStr"/>
@@ -10659,7 +11347,11 @@
           <t>RPC + statusMap</t>
         </is>
       </c>
-      <c r="J182" s="3" t="inlineStr"/>
+      <c r="J182" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K182" s="4" t="inlineStr"/>
       <c r="L182" s="3" t="inlineStr"/>
       <c r="M182" s="4" t="inlineStr"/>
@@ -10711,7 +11403,11 @@
           <t>Per-course enroll (errors non-fatal)</t>
         </is>
       </c>
-      <c r="J183" s="3" t="inlineStr"/>
+      <c r="J183" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K183" s="4" t="inlineStr"/>
       <c r="L183" s="3" t="inlineStr"/>
       <c r="M183" s="4" t="inlineStr"/>
@@ -10763,7 +11459,11 @@
           <t>Sequential awaits; verify non-fatal</t>
         </is>
       </c>
-      <c r="J184" s="3" t="inlineStr"/>
+      <c r="J184" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K184" s="4" t="inlineStr"/>
       <c r="L184" s="3" t="inlineStr"/>
       <c r="M184" s="4" t="inlineStr"/>
@@ -10815,7 +11515,11 @@
           <t>RPC link_university_email + verify</t>
         </is>
       </c>
-      <c r="J185" s="3" t="inlineStr"/>
+      <c r="J185" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K185" s="4" t="inlineStr"/>
       <c r="L185" s="3" t="inlineStr"/>
       <c r="M185" s="4" t="inlineStr"/>
@@ -10867,7 +11571,11 @@
           <t>Admin-gated; synchronous (no queue yet)</t>
         </is>
       </c>
-      <c r="J186" s="3" t="inlineStr"/>
+      <c r="J186" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K186" s="4" t="inlineStr"/>
       <c r="L186" s="3" t="inlineStr"/>
       <c r="M186" s="4" t="inlineStr"/>
@@ -10919,7 +11627,11 @@
           <t>Surfaced only in library catalog sheet, not on dashboard</t>
         </is>
       </c>
-      <c r="J187" s="3" t="inlineStr"/>
+      <c r="J187" s="26" t="inlineStr">
+        <is>
+          <t>N/A (by design)</t>
+        </is>
+      </c>
       <c r="K187" s="4" t="inlineStr"/>
       <c r="L187" s="3" t="inlineStr"/>
       <c r="M187" s="21" t="inlineStr">
@@ -10979,7 +11691,11 @@
           <t>Editor wired to same RPCs</t>
         </is>
       </c>
-      <c r="J188" s="3" t="inlineStr"/>
+      <c r="J188" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K188" s="4" t="inlineStr"/>
       <c r="L188" s="3" t="inlineStr"/>
       <c r="M188" s="4" t="inlineStr"/>
@@ -11031,7 +11747,11 @@
           <t>Wired + server RPC</t>
         </is>
       </c>
-      <c r="J189" s="3" t="inlineStr"/>
+      <c r="J189" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K189" s="4" t="inlineStr"/>
       <c r="L189" s="3" t="inlineStr"/>
       <c r="M189" s="4" t="inlineStr"/>
@@ -11083,7 +11803,11 @@
           <t>dedupe_key unique index</t>
         </is>
       </c>
-      <c r="J190" s="3" t="inlineStr"/>
+      <c r="J190" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K190" s="4" t="inlineStr"/>
       <c r="L190" s="3" t="inlineStr"/>
       <c r="M190" s="4" t="inlineStr"/>
@@ -11135,7 +11859,11 @@
           <t>Event-badge RPC + popup queue</t>
         </is>
       </c>
-      <c r="J191" s="3" t="inlineStr"/>
+      <c r="J191" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K191" s="4" t="inlineStr"/>
       <c r="L191" s="3" t="inlineStr"/>
       <c r="M191" s="4" t="inlineStr"/>
@@ -11187,7 +11915,11 @@
           <t>Event badge</t>
         </is>
       </c>
-      <c r="J192" s="3" t="inlineStr"/>
+      <c r="J192" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K192" s="4" t="inlineStr"/>
       <c r="L192" s="3" t="inlineStr"/>
       <c r="M192" s="4" t="inlineStr"/>
@@ -11239,7 +11971,11 @@
           <t>Event badge</t>
         </is>
       </c>
-      <c r="J193" s="3" t="inlineStr"/>
+      <c r="J193" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K193" s="4" t="inlineStr"/>
       <c r="L193" s="3" t="inlineStr"/>
       <c r="M193" s="4" t="inlineStr"/>
@@ -11291,7 +12027,11 @@
           <t>Server-authoritative sweep</t>
         </is>
       </c>
-      <c r="J194" s="3" t="inlineStr"/>
+      <c r="J194" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K194" s="4" t="inlineStr"/>
       <c r="L194" s="3" t="inlineStr"/>
       <c r="M194" s="4" t="inlineStr"/>
@@ -11343,7 +12083,11 @@
           <t>Broad call-site coverage</t>
         </is>
       </c>
-      <c r="J195" s="3" t="inlineStr"/>
+      <c r="J195" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K195" s="4" t="inlineStr"/>
       <c r="L195" s="3" t="inlineStr"/>
       <c r="M195" s="4" t="inlineStr"/>
@@ -11395,7 +12139,11 @@
           <t>Modal from queue</t>
         </is>
       </c>
-      <c r="J196" s="3" t="inlineStr"/>
+      <c r="J196" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K196" s="4" t="inlineStr"/>
       <c r="L196" s="3" t="inlineStr"/>
       <c r="M196" s="4" t="inlineStr"/>
@@ -11447,7 +12195,11 @@
           <t>localStorage de-dupe</t>
         </is>
       </c>
-      <c r="J197" s="3" t="inlineStr"/>
+      <c r="J197" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K197" s="4" t="inlineStr"/>
       <c r="L197" s="3" t="inlineStr"/>
       <c r="M197" s="4" t="inlineStr"/>
@@ -11499,7 +12251,11 @@
           <t>Dedupe via badge key</t>
         </is>
       </c>
-      <c r="J198" s="3" t="inlineStr"/>
+      <c r="J198" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K198" s="4" t="inlineStr"/>
       <c r="L198" s="3" t="inlineStr"/>
       <c r="M198" s="4" t="inlineStr"/>
@@ -11551,7 +12307,11 @@
           <t>Notification insert</t>
         </is>
       </c>
-      <c r="J199" s="3" t="inlineStr"/>
+      <c r="J199" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K199" s="4" t="inlineStr"/>
       <c r="L199" s="3" t="inlineStr"/>
       <c r="M199" s="4" t="inlineStr"/>
@@ -11675,7 +12435,11 @@
           <t>DB-catalog-driven</t>
         </is>
       </c>
-      <c r="J201" s="3" t="inlineStr"/>
+      <c r="J201" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K201" s="4" t="inlineStr"/>
       <c r="L201" s="3" t="inlineStr"/>
       <c r="M201" s="4" t="inlineStr"/>
@@ -11727,7 +12491,11 @@
           <t>Profile-driven</t>
         </is>
       </c>
-      <c r="J202" s="3" t="inlineStr"/>
+      <c r="J202" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K202" s="4" t="inlineStr"/>
       <c r="L202" s="3" t="inlineStr"/>
       <c r="M202" s="4" t="inlineStr"/>
@@ -11851,7 +12619,11 @@
           <t>Back-compat wrapper</t>
         </is>
       </c>
-      <c r="J204" s="3" t="inlineStr"/>
+      <c r="J204" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K204" s="4" t="inlineStr"/>
       <c r="L204" s="3" t="inlineStr"/>
       <c r="M204" s="4" t="inlineStr"/>
@@ -11903,7 +12675,11 @@
           <t>Pure resolver</t>
         </is>
       </c>
-      <c r="J205" s="3" t="inlineStr"/>
+      <c r="J205" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K205" s="4" t="inlineStr"/>
       <c r="L205" s="3" t="inlineStr"/>
       <c r="M205" s="4" t="inlineStr"/>
@@ -11955,7 +12731,11 @@
           <t>Safari-safe ring</t>
         </is>
       </c>
-      <c r="J206" s="3" t="inlineStr"/>
+      <c r="J206" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K206" s="4" t="inlineStr"/>
       <c r="L206" s="3" t="inlineStr"/>
       <c r="M206" s="4" t="inlineStr"/>
@@ -12007,7 +12787,11 @@
           <t>Profile-driven</t>
         </is>
       </c>
-      <c r="J207" s="3" t="inlineStr"/>
+      <c r="J207" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K207" s="4" t="inlineStr"/>
       <c r="L207" s="3" t="inlineStr"/>
       <c r="M207" s="4" t="inlineStr"/>
@@ -12059,7 +12843,11 @@
           <t>Used in lists/profiles</t>
         </is>
       </c>
-      <c r="J208" s="3" t="inlineStr"/>
+      <c r="J208" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K208" s="4" t="inlineStr"/>
       <c r="L208" s="3" t="inlineStr"/>
       <c r="M208" s="4" t="inlineStr"/>
@@ -12111,7 +12899,11 @@
           <t>Pure helper</t>
         </is>
       </c>
-      <c r="J209" s="3" t="inlineStr"/>
+      <c r="J209" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K209" s="4" t="inlineStr"/>
       <c r="L209" s="3" t="inlineStr"/>
       <c r="M209" s="4" t="inlineStr"/>
@@ -12163,7 +12955,11 @@
           <t>get_friends RPC</t>
         </is>
       </c>
-      <c r="J210" s="3" t="inlineStr"/>
+      <c r="J210" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K210" s="4" t="inlineStr"/>
       <c r="L210" s="3" t="inlineStr"/>
       <c r="M210" s="4" t="inlineStr"/>
@@ -12215,7 +13011,11 @@
           <t>Reciprocal auto-accept</t>
         </is>
       </c>
-      <c r="J211" s="3" t="inlineStr"/>
+      <c r="J211" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K211" s="4" t="inlineStr"/>
       <c r="L211" s="3" t="inlineStr"/>
       <c r="M211" s="4" t="inlineStr"/>
@@ -12267,7 +13067,11 @@
           <t>RPC + invalidation</t>
         </is>
       </c>
-      <c r="J212" s="3" t="inlineStr"/>
+      <c r="J212" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K212" s="4" t="inlineStr"/>
       <c r="L212" s="3" t="inlineStr"/>
       <c r="M212" s="4" t="inlineStr"/>
@@ -12319,7 +13123,11 @@
           <t>Delete pending edge</t>
         </is>
       </c>
-      <c r="J213" s="3" t="inlineStr"/>
+      <c r="J213" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K213" s="4" t="inlineStr"/>
       <c r="L213" s="3" t="inlineStr"/>
       <c r="M213" s="4" t="inlineStr"/>
@@ -12371,7 +13179,11 @@
           <t>RPC+mutation wired; no visible remove-friend UI</t>
         </is>
       </c>
-      <c r="J214" s="3" t="inlineStr"/>
+      <c r="J214" s="26" t="inlineStr">
+        <is>
+          <t>N/A (feature gap)</t>
+        </is>
+      </c>
       <c r="K214" s="4" t="inlineStr"/>
       <c r="L214" s="3" t="inlineStr"/>
       <c r="M214" s="21" t="inlineStr">
@@ -12431,7 +13243,11 @@
           <t>Enriched request RPC</t>
         </is>
       </c>
-      <c r="J215" s="3" t="inlineStr"/>
+      <c r="J215" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K215" s="4" t="inlineStr"/>
       <c r="L215" s="3" t="inlineStr"/>
       <c r="M215" s="4" t="inlineStr"/>
@@ -12483,7 +13299,11 @@
           <t>Academic-aware search</t>
         </is>
       </c>
-      <c r="J216" s="3" t="inlineStr"/>
+      <c r="J216" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K216" s="4" t="inlineStr"/>
       <c r="L216" s="3" t="inlineStr"/>
       <c r="M216" s="4" t="inlineStr"/>
@@ -12535,7 +13355,11 @@
           <t>Affinity-ranked</t>
         </is>
       </c>
-      <c r="J217" s="3" t="inlineStr"/>
+      <c r="J217" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K217" s="4" t="inlineStr"/>
       <c r="L217" s="3" t="inlineStr"/>
       <c r="M217" s="4" t="inlineStr"/>
@@ -12587,7 +13411,11 @@
           <t>Friend-gated profile</t>
         </is>
       </c>
-      <c r="J218" s="3" t="inlineStr"/>
+      <c r="J218" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K218" s="4" t="inlineStr"/>
       <c r="L218" s="3" t="inlineStr"/>
       <c r="M218" s="4" t="inlineStr"/>
@@ -12639,7 +13467,11 @@
           <t>Own-row social update</t>
         </is>
       </c>
-      <c r="J219" s="3" t="inlineStr"/>
+      <c r="J219" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K219" s="4" t="inlineStr"/>
       <c r="L219" s="3" t="inlineStr"/>
       <c r="M219" s="4" t="inlineStr"/>
@@ -12691,7 +13523,11 @@
           <t>Students-only, XP-ranked</t>
         </is>
       </c>
-      <c r="J220" s="3" t="inlineStr"/>
+      <c r="J220" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K220" s="4" t="inlineStr"/>
       <c r="L220" s="3" t="inlineStr"/>
       <c r="M220" s="4" t="inlineStr"/>
@@ -12743,7 +13579,11 @@
           <t>Client-side filters</t>
         </is>
       </c>
-      <c r="J221" s="3" t="inlineStr"/>
+      <c r="J221" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K221" s="4" t="inlineStr"/>
       <c r="L221" s="3" t="inlineStr"/>
       <c r="M221" s="4" t="inlineStr"/>
@@ -12867,7 +13707,11 @@
           <t>7-day RPC</t>
         </is>
       </c>
-      <c r="J223" s="3" t="inlineStr"/>
+      <c r="J223" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K223" s="4" t="inlineStr"/>
       <c r="L223" s="3" t="inlineStr"/>
       <c r="M223" s="4" t="inlineStr"/>
@@ -12919,7 +13763,11 @@
           <t>relationship_status RPC</t>
         </is>
       </c>
-      <c r="J224" s="3" t="inlineStr"/>
+      <c r="J224" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K224" s="4" t="inlineStr"/>
       <c r="L224" s="3" t="inlineStr"/>
       <c r="M224" s="4" t="inlineStr"/>
@@ -12971,7 +13819,11 @@
           <t>Dead path — no call site</t>
         </is>
       </c>
-      <c r="J225" s="3" t="inlineStr"/>
+      <c r="J225" s="26" t="inlineStr">
+        <is>
+          <t>N/A (dead code)</t>
+        </is>
+      </c>
       <c r="K225" s="4" t="inlineStr"/>
       <c r="L225" s="3" t="inlineStr"/>
       <c r="M225" s="21" t="inlineStr">
@@ -13031,7 +13883,11 @@
           <t>Self-redirect guard</t>
         </is>
       </c>
-      <c r="J226" s="3" t="inlineStr"/>
+      <c r="J226" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K226" s="4" t="inlineStr"/>
       <c r="L226" s="3" t="inlineStr"/>
       <c r="M226" s="4" t="inlineStr"/>
@@ -13083,7 +13939,11 @@
           <t>Real: per-userId fetch</t>
         </is>
       </c>
-      <c r="J227" s="3" t="inlineStr"/>
+      <c r="J227" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K227" s="4" t="inlineStr"/>
       <c r="L227" s="3" t="inlineStr"/>
       <c r="M227" s="4" t="inlineStr"/>
@@ -13135,7 +13995,11 @@
           <t>Real: detector engine</t>
         </is>
       </c>
-      <c r="J228" s="3" t="inlineStr"/>
+      <c r="J228" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K228" s="4" t="inlineStr"/>
       <c r="L228" s="3" t="inlineStr"/>
       <c r="M228" s="4" t="inlineStr"/>
@@ -13187,7 +14051,11 @@
           <t>Real thresholds over signals</t>
         </is>
       </c>
-      <c r="J229" s="3" t="inlineStr"/>
+      <c r="J229" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K229" s="4" t="inlineStr"/>
       <c r="L229" s="3" t="inlineStr"/>
       <c r="M229" s="4" t="inlineStr"/>
@@ -13239,7 +14107,11 @@
           <t>Ownership per endpoint</t>
         </is>
       </c>
-      <c r="J230" s="3" t="inlineStr"/>
+      <c r="J230" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K230" s="4" t="inlineStr"/>
       <c r="L230" s="3" t="inlineStr"/>
       <c r="M230" s="4" t="inlineStr"/>
@@ -13291,7 +14163,11 @@
           <t>Real aggregated SQL</t>
         </is>
       </c>
-      <c r="J231" s="3" t="inlineStr"/>
+      <c r="J231" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K231" s="4" t="inlineStr"/>
       <c r="L231" s="3" t="inlineStr"/>
       <c r="M231" s="4" t="inlineStr"/>
@@ -13343,7 +14219,11 @@
           <t>Real per-slide metrics</t>
         </is>
       </c>
-      <c r="J232" s="3" t="inlineStr"/>
+      <c r="J232" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K232" s="4" t="inlineStr"/>
       <c r="L232" s="3" t="inlineStr"/>
       <c r="M232" s="4" t="inlineStr"/>
@@ -13395,7 +14275,11 @@
           <t>Real from quiz attempts</t>
         </is>
       </c>
-      <c r="J233" s="3" t="inlineStr"/>
+      <c r="J233" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K233" s="4" t="inlineStr"/>
       <c r="L233" s="3" t="inlineStr"/>
       <c r="M233" s="4" t="inlineStr"/>
@@ -13447,7 +14331,11 @@
           <t>Real</t>
         </is>
       </c>
-      <c r="J234" s="3" t="inlineStr"/>
+      <c r="J234" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K234" s="4" t="inlineStr"/>
       <c r="L234" s="3" t="inlineStr"/>
       <c r="M234" s="4" t="inlineStr"/>
@@ -13499,7 +14387,11 @@
           <t>Real</t>
         </is>
       </c>
-      <c r="J235" s="3" t="inlineStr"/>
+      <c r="J235" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K235" s="4" t="inlineStr"/>
       <c r="L235" s="3" t="inlineStr"/>
       <c r="M235" s="4" t="inlineStr"/>
@@ -13551,7 +14443,11 @@
           <t>Real, anonymized; rule-based (not 'archetype/triad' naming)</t>
         </is>
       </c>
-      <c r="J236" s="3" t="inlineStr"/>
+      <c r="J236" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K236" s="4" t="inlineStr"/>
       <c r="L236" s="3" t="inlineStr"/>
       <c r="M236" s="4" t="inlineStr"/>
@@ -13603,7 +14499,11 @@
           <t>Real</t>
         </is>
       </c>
-      <c r="J237" s="3" t="inlineStr"/>
+      <c r="J237" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K237" s="4" t="inlineStr"/>
       <c r="L237" s="3" t="inlineStr"/>
       <c r="M237" s="4" t="inlineStr"/>
@@ -13727,7 +14627,11 @@
           <t>Real AI call + fallback</t>
         </is>
       </c>
-      <c r="J239" s="3" t="inlineStr"/>
+      <c r="J239" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K239" s="4" t="inlineStr"/>
       <c r="L239" s="3" t="inlineStr"/>
       <c r="M239" s="4" t="inlineStr"/>
@@ -13779,7 +14683,11 @@
           <t>Real intent-constrained LLM</t>
         </is>
       </c>
-      <c r="J240" s="3" t="inlineStr"/>
+      <c r="J240" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K240" s="4" t="inlineStr"/>
       <c r="L240" s="3" t="inlineStr"/>
       <c r="M240" s="4" t="inlineStr"/>
@@ -13831,7 +14739,11 @@
           <t>Real aggregated siblings</t>
         </is>
       </c>
-      <c r="J241" s="3" t="inlineStr"/>
+      <c r="J241" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K241" s="4" t="inlineStr"/>
       <c r="L241" s="3" t="inlineStr"/>
       <c r="M241" s="4" t="inlineStr"/>
@@ -13883,7 +14795,11 @@
           <t>Feature-flagged off in code</t>
         </is>
       </c>
-      <c r="J242" s="3" t="inlineStr"/>
+      <c r="J242" s="26" t="inlineStr">
+        <is>
+          <t>N/A (intentional)</t>
+        </is>
+      </c>
       <c r="K242" s="4" t="inlineStr"/>
       <c r="L242" s="3" t="inlineStr"/>
       <c r="M242" s="21" t="inlineStr">
@@ -13943,9 +14859,21 @@
           <t>Backend real; no clear consuming component found in render scan</t>
         </is>
       </c>
-      <c r="J243" s="3" t="inlineStr"/>
-      <c r="K243" s="4" t="inlineStr"/>
-      <c r="L243" s="3" t="inlineStr"/>
+      <c r="J243" s="21" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K243" s="4" t="inlineStr">
+        <is>
+          <t>Phase-1 evidence said 'no clear consuming component' — incorrect/incomplete scan. src/features/analytics/components/BenchmarksSection.tsx and analyticsService.ts do consume the distractor-analysis endpoint.</t>
+        </is>
+      </c>
+      <c r="L243" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="M243" s="4" t="inlineStr"/>
       <c r="N243" s="4" t="inlineStr"/>
     </row>
@@ -13995,7 +14923,11 @@
           <t>Real cached aggregate</t>
         </is>
       </c>
-      <c r="J244" s="3" t="inlineStr"/>
+      <c r="J244" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K244" s="4" t="inlineStr"/>
       <c r="L244" s="3" t="inlineStr"/>
       <c r="M244" s="4" t="inlineStr"/>
@@ -14047,7 +14979,11 @@
           <t>Real invalidation</t>
         </is>
       </c>
-      <c r="J245" s="3" t="inlineStr"/>
+      <c r="J245" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K245" s="4" t="inlineStr"/>
       <c r="L245" s="3" t="inlineStr"/>
       <c r="M245" s="4" t="inlineStr"/>
@@ -14099,7 +15035,11 @@
           <t>Real grounded LLM</t>
         </is>
       </c>
-      <c r="J246" s="3" t="inlineStr"/>
+      <c r="J246" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K246" s="4" t="inlineStr"/>
       <c r="L246" s="3" t="inlineStr"/>
       <c r="M246" s="4" t="inlineStr"/>
@@ -14151,7 +15091,11 @@
           <t>Real from event history</t>
         </is>
       </c>
-      <c r="J247" s="3" t="inlineStr"/>
+      <c r="J247" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K247" s="4" t="inlineStr"/>
       <c r="L247" s="3" t="inlineStr"/>
       <c r="M247" s="4" t="inlineStr"/>
@@ -14203,7 +15147,11 @@
           <t>Real metrics but canned headlines/tips; /insights route redirected away</t>
         </is>
       </c>
-      <c r="J248" s="3" t="inlineStr"/>
+      <c r="J248" s="26" t="inlineStr">
+        <is>
+          <t>N/A (minor/cosmetic)</t>
+        </is>
+      </c>
       <c r="K248" s="4" t="inlineStr"/>
       <c r="L248" s="3" t="inlineStr"/>
       <c r="M248" s="21" t="inlineStr">
@@ -14263,7 +15211,11 @@
           <t>Role-gated front+back</t>
         </is>
       </c>
-      <c r="J249" s="3" t="inlineStr"/>
+      <c r="J249" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K249" s="4" t="inlineStr"/>
       <c r="L249" s="3" t="inlineStr"/>
       <c r="M249" s="4" t="inlineStr"/>
@@ -14315,7 +15267,11 @@
           <t>Real data; role MANAGEMENT not implemented (view-only)</t>
         </is>
       </c>
-      <c r="J250" s="3" t="inlineStr"/>
+      <c r="J250" s="26" t="inlineStr">
+        <is>
+          <t>N/A (feature gap)</t>
+        </is>
+      </c>
       <c r="K250" s="4" t="inlineStr"/>
       <c r="L250" s="3" t="inlineStr"/>
       <c r="M250" s="21" t="inlineStr">
@@ -14375,7 +15331,11 @@
           <t>Real, paginated</t>
         </is>
       </c>
-      <c r="J251" s="3" t="inlineStr"/>
+      <c r="J251" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K251" s="4" t="inlineStr"/>
       <c r="L251" s="3" t="inlineStr"/>
       <c r="M251" s="4" t="inlineStr"/>
@@ -14427,7 +15387,11 @@
           <t>Real, flips is_archived</t>
         </is>
       </c>
-      <c r="J252" s="3" t="inlineStr"/>
+      <c r="J252" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K252" s="4" t="inlineStr"/>
       <c r="L252" s="3" t="inlineStr"/>
       <c r="M252" s="4" t="inlineStr"/>
@@ -14479,7 +15443,11 @@
           <t>MOCK/placeholder data unless Sentry env configured</t>
         </is>
       </c>
-      <c r="J253" s="3" t="inlineStr"/>
+      <c r="J253" s="26" t="inlineStr">
+        <is>
+          <t>N/A (config)</t>
+        </is>
+      </c>
       <c r="K253" s="4" t="inlineStr"/>
       <c r="L253" s="3" t="inlineStr"/>
       <c r="M253" s="21" t="inlineStr">
@@ -14539,7 +15507,11 @@
           <t>Real RPC (depends on stored proc)</t>
         </is>
       </c>
-      <c r="J254" s="3" t="inlineStr"/>
+      <c r="J254" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K254" s="4" t="inlineStr"/>
       <c r="L254" s="3" t="inlineStr"/>
       <c r="M254" s="4" t="inlineStr"/>
@@ -14591,7 +15563,11 @@
           <t>Real (depends on analytics_backups + RPCs)</t>
         </is>
       </c>
-      <c r="J255" s="3" t="inlineStr"/>
+      <c r="J255" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K255" s="4" t="inlineStr"/>
       <c r="L255" s="3" t="inlineStr"/>
       <c r="M255" s="4" t="inlineStr"/>
@@ -14643,7 +15619,11 @@
           <t>Mostly real; app_version '0.1.0-alpha' + pool sizes hardcoded strings</t>
         </is>
       </c>
-      <c r="J256" s="3" t="inlineStr"/>
+      <c r="J256" s="26" t="inlineStr">
+        <is>
+          <t>N/A (cosmetic)</t>
+        </is>
+      </c>
       <c r="K256" s="4" t="inlineStr"/>
       <c r="L256" s="3" t="inlineStr"/>
       <c r="M256" s="21" t="inlineStr">
@@ -14703,7 +15683,11 @@
           <t>Real insert to user_feedback</t>
         </is>
       </c>
-      <c r="J257" s="3" t="inlineStr"/>
+      <c r="J257" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K257" s="4" t="inlineStr"/>
       <c r="L257" s="3" t="inlineStr"/>
       <c r="M257" s="4" t="inlineStr"/>
@@ -14755,7 +15739,11 @@
           <t>Hidden on auth/landing</t>
         </is>
       </c>
-      <c r="J258" s="3" t="inlineStr"/>
+      <c r="J258" s="21" t="inlineStr">
+        <is>
+          <t>PASS (static: Key Files verified present on main 2026-07-18 + full automated suite green — backend 1159 non-db tests, frontend 419, tsc 0 errors. Not a live/browser-driven QA pass.)</t>
+        </is>
+      </c>
       <c r="K258" s="4" t="inlineStr"/>
       <c r="L258" s="3" t="inlineStr"/>
       <c r="M258" s="4" t="inlineStr"/>
@@ -14807,7 +15795,11 @@
           <t>Write-only; no review surface</t>
         </is>
       </c>
-      <c r="J259" s="3" t="inlineStr"/>
+      <c r="J259" s="26" t="inlineStr">
+        <is>
+          <t>N/A (feature gap)</t>
+        </is>
+      </c>
       <c r="K259" s="4" t="inlineStr"/>
       <c r="L259" s="3" t="inlineStr"/>
       <c r="M259" s="21" t="inlineStr">
@@ -15295,7 +16287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -15926,6 +16918,114 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B24" s="24" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C24" s="24" t="inlineStr">
+        <is>
+          <t>BASELINE: full suites re-run</t>
+        </is>
+      </c>
+      <c r="D24" s="24" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="E24" s="24" t="inlineStr">
+        <is>
+          <t>Backend non-db 1159 passed / 0 fail (backend/venv has no pytest — corrected interpreter to .venv/bin/python; backend db-fixture tests error without a live Postgres connection in this sandbox, expected/environmental, not a regression); frontend vitest 419 passed / 0 fail; tsc --noEmit 0 errors.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B25" s="24" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C25" s="24" t="inlineStr">
+        <is>
+          <t>RETEST: AI-01/AI-21/PDF-05/PDF-27 gap</t>
+        </is>
+      </c>
+      <c r="D25" s="24" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="E25" s="24" t="inlineStr">
+        <is>
+          <t>4 stories had Fix Applied(P3) but no Retest(P4) recorded. AI-01/AI-21: re-verified tutor.py has no orphaned returns + test_tutor_grounding 7/7 pass → PASS. PDF-05/PDF-27: stamped N/A since both are deferred with no code change to retest.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B26" s="24" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C26" s="24" t="inlineStr">
+        <is>
+          <t>AUDIT: 224 untested stories investigated</t>
+        </is>
+      </c>
+      <c r="D26" s="24" t="inlineStr">
+        <is>
+          <t>12 DRIFT FOUND</t>
+        </is>
+      </c>
+      <c r="E26" s="24" t="inlineStr">
+        <is>
+          <t>Every story lacking a Test Result(P2) stamp was cross-checked: Key Files existence verified against current `main`, Code Status validated. Surfaced 12 cases of audit drift since the 2026-06-24 Phase-1 snapshot — all documentation corrections, not code defects: PDF-22/24/25 (Fast Upload retired — fast_upload.py archived to backend/_legacy/, unmounted, FastUpload.tsx removed, no route); PDF-20/21 (LectureEdit.tsx merged into LectureUpload.tsx isEditMode, still live); AUTH-14 (routeGuards.tsx deleted per AUTH-15, logic now lives in App.tsx ProtectedRoute, matches); AUTH-32/33 (UniversityEmailLink/AcademicProfileEditor moved from Settings.tsx to Ascent.tsx/Onboarding.tsx); PDF-32 (ad-hoc debug scripts already deleted); AI-19/ANL-17 (Phase-1 'no frontend caller found' was an incomplete scan — both are actually wired up: useTTS in 3 components, distractor analysis in BenchmarksSection). CRS-21 re-confirmed still true (direct Supabase reads bypass enrollment filter) — no product decision made, left Partial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B27" s="24" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C27" s="24" t="inlineStr">
+        <is>
+          <t>BATCH: static+suite verification</t>
+        </is>
+      </c>
+      <c r="D27" s="24" t="inlineStr">
+        <is>
+          <t>SEE SCRIPT OUTPUT</t>
+        </is>
+      </c>
+      <c r="E27" s="24" t="inlineStr">
+        <is>
+          <t>The remaining 'Functioning' stories with no per-row drift were batch-stamped PASS via update_results.py's programmatic pass: Key Files existence checked against `git ls-files`, cross-referenced with the green automated suites. Explicitly NOT equivalent to a live/browser-driven QA pass — that still requires a real authenticated Supabase+Redis stack, a known constraint carried from Phase 2/4 (2026-06-24/29).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
